--- a/listas/output/Lista Amarilla.xlsx
+++ b/listas/output/Lista Amarilla.xlsx
@@ -43,7 +43,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Puertas Livianas'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'Puertas Placa'!$A1:$F32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'Puertas Placa'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'Recargos'!$A1:$C68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'Recargos'!$A1:$C69</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Recargos'!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="316">
   <si>
     <t>VENTANAS HERRERO</t>
   </si>
@@ -810,6 +810,12 @@
   </si>
   <si>
     <t>20%</t>
+  </si>
+  <si>
+    <t>RECARGO Tres Guias</t>
+  </si>
+  <si>
+    <t>25%</t>
   </si>
   <si>
     <t>RECARGO Natural</t>
@@ -2056,16 +2062,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="4">
-        <v>31264</v>
+        <v>32672</v>
       </c>
       <c r="C6" s="4">
-        <v>40168</v>
+        <v>41575</v>
       </c>
       <c r="D6" s="4">
         <v>14743</v>
       </c>
       <c r="E6" s="4">
-        <v>40644</v>
+        <v>42473</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2073,16 +2079,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="4">
-        <v>44567</v>
+        <v>44800</v>
       </c>
       <c r="C7" s="4">
-        <v>53470</v>
+        <v>53703</v>
       </c>
       <c r="D7" s="4">
         <v>16545</v>
       </c>
       <c r="E7" s="4">
-        <v>57937</v>
+        <v>58240</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2090,16 +2096,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="4">
-        <v>48967</v>
+        <v>49266</v>
       </c>
       <c r="C8" s="4">
-        <v>57870</v>
+        <v>58169</v>
       </c>
       <c r="D8" s="4">
         <v>18970</v>
       </c>
       <c r="E8" s="4">
-        <v>63657</v>
+        <v>64045</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2107,16 +2113,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="4">
-        <v>54827</v>
+        <v>55193</v>
       </c>
       <c r="C9" s="4">
-        <v>63730</v>
+        <v>64096</v>
       </c>
       <c r="D9" s="4">
         <v>21394</v>
       </c>
       <c r="E9" s="4">
-        <v>71274</v>
+        <v>71751</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2124,16 +2130,16 @@
         <v>10</v>
       </c>
       <c r="B10" s="4">
-        <v>64297</v>
+        <v>64762</v>
       </c>
       <c r="C10" s="4">
-        <v>73200</v>
+        <v>73665</v>
       </c>
       <c r="D10" s="4">
         <v>25031</v>
       </c>
       <c r="E10" s="4">
-        <v>83586</v>
+        <v>84191</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2141,16 +2147,16 @@
         <v>11</v>
       </c>
       <c r="B11" s="4">
-        <v>72351</v>
+        <v>72915</v>
       </c>
       <c r="C11" s="4">
-        <v>81254</v>
+        <v>81818</v>
       </c>
       <c r="D11" s="4">
         <v>28667</v>
       </c>
       <c r="E11" s="4">
-        <v>94056</v>
+        <v>94790</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2158,16 +2164,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="4">
-        <v>80354</v>
+        <v>80985</v>
       </c>
       <c r="C12" s="4">
-        <v>89257</v>
+        <v>89888</v>
       </c>
       <c r="D12" s="4">
         <v>31093</v>
       </c>
       <c r="E12" s="4">
-        <v>104460</v>
+        <v>105281</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2175,16 +2181,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="4">
-        <v>44317</v>
+        <v>44595</v>
       </c>
       <c r="C13" s="4">
-        <v>57672</v>
+        <v>57950</v>
       </c>
       <c r="D13" s="4">
         <v>18613</v>
       </c>
       <c r="E13" s="4">
-        <v>57612</v>
+        <v>57973</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2192,16 +2198,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="4">
-        <v>54656</v>
+        <v>55044</v>
       </c>
       <c r="C14" s="4">
-        <v>68010</v>
+        <v>68398</v>
       </c>
       <c r="D14" s="4">
         <v>21394</v>
       </c>
       <c r="E14" s="4">
-        <v>71052</v>
+        <v>71557</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2209,16 +2215,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="4">
-        <v>60854</v>
+        <v>61353</v>
       </c>
       <c r="C15" s="4">
-        <v>74209</v>
+        <v>74707</v>
       </c>
       <c r="D15" s="4">
         <v>24175</v>
       </c>
       <c r="E15" s="4">
-        <v>79110</v>
+        <v>79759</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2226,16 +2232,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="4">
-        <v>67414</v>
+        <v>68022</v>
       </c>
       <c r="C16" s="4">
-        <v>80768</v>
+        <v>81377</v>
       </c>
       <c r="D16" s="4">
         <v>26956</v>
       </c>
       <c r="E16" s="4">
-        <v>87637</v>
+        <v>88429</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2243,16 +2249,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>78249</v>
+        <v>79024</v>
       </c>
       <c r="C17" s="4">
-        <v>91604</v>
+        <v>92379</v>
       </c>
       <c r="D17" s="4">
         <v>31128</v>
       </c>
       <c r="E17" s="4">
-        <v>101724</v>
+        <v>102732</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2260,16 +2266,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>87635</v>
+        <v>88576</v>
       </c>
       <c r="C18" s="4">
-        <v>100989</v>
+        <v>101931</v>
       </c>
       <c r="D18" s="4">
         <v>35300</v>
       </c>
       <c r="E18" s="4">
-        <v>113926</v>
+        <v>115149</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2277,16 +2283,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>99734</v>
+        <v>100787</v>
       </c>
       <c r="C19" s="4">
-        <v>113089</v>
+        <v>114142</v>
       </c>
       <c r="D19" s="4">
         <v>38081</v>
       </c>
       <c r="E19" s="4">
-        <v>129654</v>
+        <v>131023</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2294,16 +2300,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="4">
-        <v>75266</v>
+        <v>75965</v>
       </c>
       <c r="C20" s="4">
-        <v>93073</v>
+        <v>93772</v>
       </c>
       <c r="D20" s="4">
         <v>29382</v>
       </c>
       <c r="E20" s="4">
-        <v>97847</v>
+        <v>98755</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2311,16 +2317,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="4">
-        <v>82184</v>
+        <v>83038</v>
       </c>
       <c r="C21" s="4">
-        <v>99991</v>
+        <v>100844</v>
       </c>
       <c r="D21" s="4">
         <v>32518</v>
       </c>
       <c r="E21" s="4">
-        <v>106840</v>
+        <v>107949</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2328,16 +2334,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="4">
-        <v>94352</v>
+        <v>95437</v>
       </c>
       <c r="C22" s="4">
-        <v>112159</v>
+        <v>113244</v>
       </c>
       <c r="D22" s="4">
         <v>37226</v>
       </c>
       <c r="E22" s="4">
-        <v>122657</v>
+        <v>124068</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2345,16 +2351,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="4">
-        <v>104367</v>
+        <v>105684</v>
       </c>
       <c r="C23" s="4">
-        <v>122173</v>
+        <v>123490</v>
       </c>
       <c r="D23" s="4">
         <v>41932</v>
       </c>
       <c r="E23" s="4">
-        <v>135677</v>
+        <v>137389</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2362,16 +2368,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="4">
-        <v>117761</v>
+        <v>119234</v>
       </c>
       <c r="C24" s="4">
-        <v>135568</v>
+        <v>137041</v>
       </c>
       <c r="D24" s="4">
         <v>45070</v>
       </c>
       <c r="E24" s="4">
-        <v>153089</v>
+        <v>155004</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2379,16 +2385,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="4">
-        <v>86960</v>
+        <v>87857</v>
       </c>
       <c r="C25" s="4">
-        <v>109217</v>
+        <v>110114</v>
       </c>
       <c r="D25" s="4">
         <v>34587</v>
       </c>
       <c r="E25" s="4">
-        <v>113048</v>
+        <v>114214</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2396,16 +2402,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="4">
-        <v>94483</v>
+        <v>95580</v>
       </c>
       <c r="C26" s="4">
-        <v>116740</v>
+        <v>117836</v>
       </c>
       <c r="D26" s="4">
         <v>38081</v>
       </c>
       <c r="E26" s="4">
-        <v>122828</v>
+        <v>124253</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2413,16 +2419,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="4">
-        <v>108282</v>
+        <v>109677</v>
       </c>
       <c r="C27" s="4">
-        <v>130538</v>
+        <v>131934</v>
       </c>
       <c r="D27" s="4">
         <v>43322</v>
       </c>
       <c r="E27" s="4">
-        <v>140766</v>
+        <v>142581</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2430,16 +2436,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="4">
-        <v>119626</v>
+        <v>121320</v>
       </c>
       <c r="C28" s="4">
-        <v>141883</v>
+        <v>143577</v>
       </c>
       <c r="D28" s="4">
         <v>48564</v>
       </c>
       <c r="E28" s="4">
-        <v>155514</v>
+        <v>157716</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2447,16 +2453,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="4">
-        <v>133929</v>
+        <v>135823</v>
       </c>
       <c r="C29" s="4">
-        <v>156186</v>
+        <v>158080</v>
       </c>
       <c r="D29" s="4">
         <v>52059</v>
       </c>
       <c r="E29" s="4">
-        <v>174108</v>
+        <v>176570</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2464,16 +2470,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="4">
-        <v>141013</v>
+        <v>143107</v>
       </c>
       <c r="C30" s="4">
-        <v>163270</v>
+        <v>165363</v>
       </c>
       <c r="D30" s="4">
         <v>55553</v>
       </c>
       <c r="E30" s="4">
-        <v>183318</v>
+        <v>186039</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2481,16 +2487,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="4">
-        <v>149537</v>
+        <v>151830</v>
       </c>
       <c r="C31" s="4">
-        <v>171794</v>
+        <v>174087</v>
       </c>
       <c r="D31" s="4">
         <v>59047</v>
       </c>
       <c r="E31" s="4">
-        <v>194399</v>
+        <v>197379</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2498,16 +2504,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="4">
-        <v>93552</v>
+        <v>94549</v>
       </c>
       <c r="C32" s="4">
-        <v>118035</v>
+        <v>119032</v>
       </c>
       <c r="D32" s="4">
         <v>37189</v>
       </c>
       <c r="E32" s="4">
-        <v>121618</v>
+        <v>122914</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2515,16 +2521,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="4">
-        <v>102516</v>
+        <v>103735</v>
       </c>
       <c r="C33" s="4">
-        <v>126999</v>
+        <v>128218</v>
       </c>
       <c r="D33" s="4">
         <v>40863</v>
       </c>
       <c r="E33" s="4">
-        <v>133271</v>
+        <v>134856</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2532,16 +2538,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="4">
-        <v>116772</v>
+        <v>118323</v>
       </c>
       <c r="C34" s="4">
-        <v>141255</v>
+        <v>142805</v>
       </c>
       <c r="D34" s="4">
         <v>46372</v>
       </c>
       <c r="E34" s="4">
-        <v>151804</v>
+        <v>153820</v>
       </c>
     </row>
     <row r="35" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2549,16 +2555,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="4">
-        <v>129518</v>
+        <v>131402</v>
       </c>
       <c r="C35" s="4">
-        <v>154001</v>
+        <v>155884</v>
       </c>
       <c r="D35" s="4">
         <v>51881</v>
       </c>
       <c r="E35" s="4">
-        <v>168373</v>
+        <v>170823</v>
       </c>
     </row>
     <row r="36" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2566,16 +2572,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="4">
-        <v>151975</v>
+        <v>154301</v>
       </c>
       <c r="C36" s="4">
-        <v>176458</v>
+        <v>178784</v>
       </c>
       <c r="D36" s="4">
         <v>62898</v>
       </c>
       <c r="E36" s="4">
-        <v>197568</v>
+        <v>200591</v>
       </c>
     </row>
     <row r="37" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2583,16 +2589,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="4">
-        <v>156448</v>
+        <v>158995</v>
       </c>
       <c r="C37" s="4">
-        <v>180930</v>
+        <v>183478</v>
       </c>
       <c r="D37" s="4">
         <v>62898</v>
       </c>
       <c r="E37" s="4">
-        <v>203382</v>
+        <v>206693</v>
       </c>
     </row>
     <row r="38" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2600,16 +2606,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="4">
-        <v>98750</v>
+        <v>99846</v>
       </c>
       <c r="C38" s="4">
-        <v>125457</v>
+        <v>126554</v>
       </c>
       <c r="D38" s="4">
         <v>39793</v>
       </c>
       <c r="E38" s="4">
-        <v>128374</v>
+        <v>129799</v>
       </c>
     </row>
     <row r="39" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2617,16 +2623,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="4">
-        <v>108167</v>
+        <v>109506</v>
       </c>
       <c r="C39" s="4">
-        <v>134874</v>
+        <v>136214</v>
       </c>
       <c r="D39" s="4">
         <v>43644</v>
       </c>
       <c r="E39" s="4">
-        <v>140616</v>
+        <v>142358</v>
       </c>
     </row>
     <row r="40" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2634,16 +2640,16 @@
         <v>40</v>
       </c>
       <c r="B40" s="4">
-        <v>123024</v>
+        <v>124729</v>
       </c>
       <c r="C40" s="4">
-        <v>149732</v>
+        <v>151437</v>
       </c>
       <c r="D40" s="4">
         <v>49420</v>
       </c>
       <c r="E40" s="4">
-        <v>159931</v>
+        <v>162149</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2651,16 +2657,16 @@
         <v>41</v>
       </c>
       <c r="B41" s="4">
-        <v>136432</v>
+        <v>138503</v>
       </c>
       <c r="C41" s="4">
-        <v>163140</v>
+        <v>165211</v>
       </c>
       <c r="D41" s="4">
         <v>55196</v>
       </c>
       <c r="E41" s="4">
-        <v>177361</v>
+        <v>180053</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2668,16 +2674,16 @@
         <v>42</v>
       </c>
       <c r="B42" s="4">
-        <v>150121</v>
+        <v>152435</v>
       </c>
       <c r="C42" s="4">
-        <v>176829</v>
+        <v>179143</v>
       </c>
       <c r="D42" s="4">
         <v>59047</v>
       </c>
       <c r="E42" s="4">
-        <v>195158</v>
+        <v>198167</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2685,16 +2691,16 @@
         <v>43</v>
       </c>
       <c r="B43" s="4">
-        <v>159609</v>
+        <v>162167</v>
       </c>
       <c r="C43" s="4">
-        <v>186316</v>
+        <v>188875</v>
       </c>
       <c r="D43" s="4">
         <v>62898</v>
       </c>
       <c r="E43" s="4">
-        <v>207492</v>
+        <v>210818</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2702,16 +2708,16 @@
         <v>44</v>
       </c>
       <c r="B44" s="4">
-        <v>167220</v>
+        <v>170023</v>
       </c>
       <c r="C44" s="4">
-        <v>193928</v>
+        <v>196730</v>
       </c>
       <c r="D44" s="4">
         <v>66749</v>
       </c>
       <c r="E44" s="4">
-        <v>217386</v>
+        <v>221030</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2719,16 +2725,16 @@
         <v>45</v>
       </c>
       <c r="B45" s="4">
-        <v>115513</v>
+        <v>116909</v>
       </c>
       <c r="C45" s="4">
-        <v>148898</v>
+        <v>150294</v>
       </c>
       <c r="D45" s="4">
         <v>47602</v>
       </c>
       <c r="E45" s="4">
-        <v>150167</v>
+        <v>151982</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2736,16 +2742,16 @@
         <v>46</v>
       </c>
       <c r="B46" s="4">
-        <v>126280</v>
+        <v>127985</v>
       </c>
       <c r="C46" s="4">
-        <v>159665</v>
+        <v>161370</v>
       </c>
       <c r="D46" s="4">
         <v>51988</v>
       </c>
       <c r="E46" s="4">
-        <v>164164</v>
+        <v>166380</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2753,16 +2759,16 @@
         <v>47</v>
       </c>
       <c r="B47" s="4">
-        <v>143140</v>
+        <v>145311</v>
       </c>
       <c r="C47" s="4">
-        <v>176525</v>
+        <v>178695</v>
       </c>
       <c r="D47" s="4">
         <v>58566</v>
       </c>
       <c r="E47" s="4">
-        <v>186082</v>
+        <v>188904</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2770,16 +2776,16 @@
         <v>48</v>
       </c>
       <c r="B48" s="4">
-        <v>157127</v>
+        <v>159763</v>
       </c>
       <c r="C48" s="4">
-        <v>190512</v>
+        <v>193148</v>
       </c>
       <c r="D48" s="4">
         <v>65145</v>
       </c>
       <c r="E48" s="4">
-        <v>204266</v>
+        <v>207691</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2787,16 +2793,16 @@
         <v>49</v>
       </c>
       <c r="B49" s="4">
-        <v>173221</v>
+        <v>176167</v>
       </c>
       <c r="C49" s="4">
-        <v>206606</v>
+        <v>209552</v>
       </c>
       <c r="D49" s="4">
         <v>69531</v>
       </c>
       <c r="E49" s="4">
-        <v>225188</v>
+        <v>229017</v>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2804,16 +2810,16 @@
         <v>50</v>
       </c>
       <c r="B50" s="4">
-        <v>182977</v>
+        <v>186232</v>
       </c>
       <c r="C50" s="4">
-        <v>216362</v>
+        <v>219617</v>
       </c>
       <c r="D50" s="4">
         <v>73916</v>
       </c>
       <c r="E50" s="4">
-        <v>237869</v>
+        <v>242102</v>
       </c>
     </row>
     <row r="51" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2821,16 +2827,16 @@
         <v>51</v>
       </c>
       <c r="B51" s="4">
-        <v>193748</v>
+        <v>197315</v>
       </c>
       <c r="C51" s="4">
-        <v>227133</v>
+        <v>230700</v>
       </c>
       <c r="D51" s="4">
         <v>78303</v>
       </c>
       <c r="E51" s="4">
-        <v>251872</v>
+        <v>256509</v>
       </c>
     </row>
     <row r="52" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2838,16 +2844,16 @@
         <v>52</v>
       </c>
       <c r="B52" s="4">
-        <v>151076</v>
+        <v>152970</v>
       </c>
       <c r="C52" s="4">
-        <v>195591</v>
+        <v>197484</v>
       </c>
       <c r="D52" s="4">
         <v>60616</v>
       </c>
       <c r="E52" s="4">
-        <v>196399</v>
+        <v>198861</v>
       </c>
     </row>
     <row r="53" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2855,16 +2861,16 @@
         <v>53</v>
       </c>
       <c r="B53" s="4">
-        <v>167557</v>
+        <v>169871</v>
       </c>
       <c r="C53" s="4">
-        <v>212072</v>
+        <v>214386</v>
       </c>
       <c r="D53" s="4">
         <v>65893</v>
       </c>
       <c r="E53" s="4">
-        <v>217825</v>
+        <v>220832</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2872,16 +2878,16 @@
         <v>54</v>
       </c>
       <c r="B54" s="4">
-        <v>194995</v>
+        <v>198096</v>
       </c>
       <c r="C54" s="4">
-        <v>239510</v>
+        <v>242610</v>
       </c>
       <c r="D54" s="4">
         <v>73809</v>
       </c>
       <c r="E54" s="4">
-        <v>253494</v>
+        <v>257525</v>
       </c>
     </row>
     <row r="55" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2889,16 +2895,16 @@
         <v>55</v>
       </c>
       <c r="B55" s="4">
-        <v>218018</v>
+        <v>221784</v>
       </c>
       <c r="C55" s="4">
-        <v>262533</v>
+        <v>266298</v>
       </c>
       <c r="D55" s="4">
         <v>81725</v>
       </c>
       <c r="E55" s="4">
-        <v>283424</v>
+        <v>288319</v>
       </c>
     </row>
     <row r="56" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2906,16 +2912,16 @@
         <v>56</v>
       </c>
       <c r="B56" s="4">
-        <v>236135</v>
+        <v>240345</v>
       </c>
       <c r="C56" s="4">
-        <v>280650</v>
+        <v>284859</v>
       </c>
       <c r="D56" s="4">
         <v>87002</v>
       </c>
       <c r="E56" s="4">
-        <v>306976</v>
+        <v>312449</v>
       </c>
     </row>
     <row r="57" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2923,16 +2929,16 @@
         <v>57</v>
       </c>
       <c r="B57" s="4">
-        <v>254163</v>
+        <v>258814</v>
       </c>
       <c r="C57" s="4">
-        <v>298677</v>
+        <v>303328</v>
       </c>
       <c r="D57" s="4">
         <v>92280</v>
       </c>
       <c r="E57" s="4">
-        <v>330412</v>
+        <v>336458</v>
       </c>
     </row>
     <row r="58" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2940,16 +2946,16 @@
         <v>58</v>
       </c>
       <c r="B58" s="4">
-        <v>269345</v>
+        <v>274440</v>
       </c>
       <c r="C58" s="4">
-        <v>313860</v>
+        <v>318955</v>
       </c>
       <c r="D58" s="4">
         <v>97557</v>
       </c>
       <c r="E58" s="4">
-        <v>350149</v>
+        <v>356772</v>
       </c>
     </row>
     <row r="59" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2957,16 +2963,16 @@
         <v>59</v>
       </c>
       <c r="B59" s="4">
-        <v>282813</v>
+        <v>288162</v>
       </c>
       <c r="C59" s="4">
-        <v>329553</v>
+        <v>334902</v>
       </c>
       <c r="D59" s="4">
         <v>102435</v>
       </c>
       <c r="E59" s="4">
-        <v>367656</v>
+        <v>374610</v>
       </c>
     </row>
   </sheetData>
@@ -3733,10 +3739,10 @@
         <v>169</v>
       </c>
       <c r="C6" s="4">
-        <v>177788</v>
+        <v>179536</v>
       </c>
       <c r="D6" s="4">
-        <v>181155</v>
+        <v>183078</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3747,10 +3753,10 @@
         <v>169</v>
       </c>
       <c r="C7" s="4">
-        <v>164033</v>
+        <v>163938</v>
       </c>
       <c r="D7" s="4">
-        <v>167400</v>
+        <v>167283</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3758,13 +3764,13 @@
         <v>172</v>
       </c>
       <c r="B8" s="4">
-        <v>187291</v>
+        <v>187975</v>
       </c>
       <c r="C8" s="4">
-        <v>190068</v>
+        <v>190897</v>
       </c>
       <c r="D8" s="4">
-        <v>191657</v>
+        <v>192568</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3772,13 +3778,13 @@
         <v>226</v>
       </c>
       <c r="B9" s="4">
-        <v>221477</v>
+        <v>222161</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>169</v>
       </c>
       <c r="D9" s="4">
-        <v>225843</v>
+        <v>226754</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3786,13 +3792,13 @@
         <v>174</v>
       </c>
       <c r="B10" s="4">
-        <v>203117</v>
+        <v>203499</v>
       </c>
       <c r="C10" s="4">
-        <v>204613</v>
+        <v>205073</v>
       </c>
       <c r="D10" s="4">
-        <v>205501</v>
+        <v>206008</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3800,13 +3806,13 @@
         <v>175</v>
       </c>
       <c r="B11" s="4">
-        <v>220448</v>
+        <v>220830</v>
       </c>
       <c r="C11" s="4">
-        <v>221944</v>
+        <v>222404</v>
       </c>
       <c r="D11" s="4">
-        <v>222832</v>
+        <v>223339</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3893,10 +3899,10 @@
         <v>235</v>
       </c>
       <c r="D6" s="4">
-        <v>99190</v>
+        <v>104260</v>
       </c>
       <c r="E6" s="4">
-        <v>105430</v>
+        <v>110760</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>169</v>
@@ -3913,10 +3919,10 @@
         <v>236</v>
       </c>
       <c r="D7" s="4">
-        <v>99190</v>
+        <v>104260</v>
       </c>
       <c r="E7" s="4">
-        <v>105430</v>
+        <v>110760</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>169</v>
@@ -3933,10 +3939,10 @@
         <v>237</v>
       </c>
       <c r="D8" s="4">
-        <v>105430</v>
+        <v>110760</v>
       </c>
       <c r="E8" s="4">
-        <v>111946</v>
+        <v>117546</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>169</v>
@@ -4079,7 +4085,7 @@
         <v>169</v>
       </c>
       <c r="F15" s="4">
-        <v>103350</v>
+        <v>108550</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4099,7 +4105,7 @@
         <v>169</v>
       </c>
       <c r="F16" s="4">
-        <v>103350</v>
+        <v>108550</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4119,7 +4125,7 @@
         <v>169</v>
       </c>
       <c r="F17" s="4">
-        <v>107380</v>
+        <v>112749</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4193,10 +4199,10 @@
         <v>235</v>
       </c>
       <c r="D21" s="4">
-        <v>297570</v>
+        <v>312449</v>
       </c>
       <c r="E21" s="4">
-        <v>297570</v>
+        <v>312449</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>169</v>
@@ -4213,10 +4219,10 @@
         <v>236</v>
       </c>
       <c r="D22" s="4">
-        <v>297570</v>
+        <v>312449</v>
       </c>
       <c r="E22" s="4">
-        <v>297570</v>
+        <v>312449</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>169</v>
@@ -4233,10 +4239,10 @@
         <v>237</v>
       </c>
       <c r="D23" s="4">
-        <v>317850</v>
+        <v>333743</v>
       </c>
       <c r="E23" s="4">
-        <v>317850</v>
+        <v>333743</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>169</v>
@@ -4378,7 +4384,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="13" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -4459,18 +4465,18 @@
         <v>249</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>249</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4478,334 +4484,334 @@
         <v>260</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C12" s="4">
-        <v>14724</v>
+        <v>249</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C13" s="4">
-        <v>24914</v>
+        <v>14724</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C14" s="4">
-        <v>10197</v>
+        <v>25661</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C15" s="4">
-        <v>5788</v>
+        <v>10473</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C16" s="4">
-        <v>18626</v>
+        <v>6063</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C17" s="4">
-        <v>28256</v>
+        <v>18626</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C18" s="4">
-        <v>8137</v>
+        <v>29103</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C19" s="4">
-        <v>25493</v>
+        <v>8137</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C20" s="4">
-        <v>66646</v>
+        <v>26871</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C21" s="4">
-        <v>477980</v>
+        <v>66646</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C22" s="4">
-        <v>386646</v>
+        <v>477980</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C23" s="4">
-        <v>477980</v>
+        <v>386646</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C24" s="4">
-        <v>41627</v>
+        <v>477980</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C25" s="4">
-        <v>31942</v>
+        <v>41627</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C26" s="4">
-        <v>51551</v>
+        <v>31942</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C27" s="4">
-        <v>38946</v>
+        <v>51551</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C28" s="4">
-        <v>72581</v>
+        <v>38946</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C29" s="4">
-        <v>53878</v>
+        <v>72581</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C30" s="4">
-        <v>260098</v>
+        <v>53878</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C31" s="4">
-        <v>192715</v>
+        <v>260098</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C32" s="4">
-        <v>281122</v>
+        <v>192715</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C33" s="4">
-        <v>213739</v>
+        <v>281122</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C34" s="4">
-        <v>34450</v>
+        <v>213739</v>
       </c>
     </row>
     <row r="35" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C35" s="4">
-        <v>62010</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="36" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C36" s="4">
-        <v>137800</v>
+        <v>62010</v>
       </c>
     </row>
     <row r="37" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C37" s="4">
-        <v>5512</v>
+        <v>137800</v>
       </c>
     </row>
     <row r="38" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C38" s="4">
-        <v>5512</v>
+        <v>9646</v>
       </c>
     </row>
     <row r="39" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C39" s="4">
-        <v>5512</v>
+        <v>9646</v>
       </c>
     </row>
     <row r="40" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C40" s="4">
-        <v>6890</v>
+        <v>9646</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C41" s="4">
-        <v>24804</v>
+        <v>9646</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>247</v>
@@ -4816,117 +4822,117 @@
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C43" s="4">
-        <v>757900</v>
+        <v>24804</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C44" s="4">
-        <v>551200</v>
+        <v>757900</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C45" s="4">
-        <v>1171300</v>
+        <v>551200</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C46" s="4">
-        <v>826800</v>
+        <v>1171300</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C47" s="4">
-        <v>6201</v>
+        <v>826800</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C48" s="4">
-        <v>344500</v>
+        <v>11024</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C49" s="4">
-        <v>6890</v>
+        <v>344500</v>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C50" s="4">
-        <v>17914</v>
+        <v>8268</v>
       </c>
     </row>
     <row r="51" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C51" s="4">
-        <v>15847</v>
+        <v>19292</v>
       </c>
     </row>
     <row r="52" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C52" s="4">
-        <v>0</v>
+        <v>18190</v>
       </c>
     </row>
     <row r="53" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>247</v>
@@ -4937,133 +4943,144 @@
     </row>
     <row r="54" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C54" s="4">
-        <v>140515</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C55" s="4">
-        <v>154566</v>
+        <v>140515</v>
       </c>
     </row>
     <row r="56" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C56" s="4">
-        <v>24042</v>
+        <v>154566</v>
       </c>
     </row>
     <row r="57" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C57" s="4">
-        <v>31039</v>
+        <v>25244</v>
       </c>
     </row>
     <row r="58" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C58" s="4">
-        <v>39685</v>
+        <v>32591</v>
       </c>
     </row>
     <row r="59" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C59" s="4">
-        <v>48802</v>
+        <v>41669</v>
       </c>
     </row>
     <row r="60" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C60" s="4">
-        <v>39456</v>
+        <v>51242</v>
       </c>
     </row>
     <row r="61" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C61" s="4">
-        <v>88805</v>
+        <v>41430</v>
       </c>
     </row>
     <row r="62" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C62" s="4">
-        <v>95742</v>
+        <v>93245</v>
       </c>
     </row>
     <row r="63" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C63" s="4">
-        <v>106952</v>
+        <v>99572</v>
       </c>
     </row>
     <row r="64" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C64" s="4">
-        <v>129380</v>
+        <v>111231</v>
       </c>
     </row>
     <row r="65" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C65" s="4">
+        <v>134556</v>
+      </c>
+    </row>
+    <row r="66" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C66" s="4">
         <v>17363</v>
       </c>
     </row>
@@ -5608,22 +5625,22 @@
         <v>99</v>
       </c>
       <c r="B6" s="4">
-        <v>43091</v>
+        <v>43256</v>
       </c>
       <c r="C6" s="4">
-        <v>43773</v>
+        <v>43971</v>
       </c>
       <c r="D6" s="4">
-        <v>45009</v>
+        <v>45272</v>
       </c>
       <c r="E6" s="4">
-        <v>50995</v>
+        <v>51563</v>
       </c>
       <c r="F6" s="4">
-        <v>44164</v>
+        <v>44383</v>
       </c>
       <c r="G6" s="4">
-        <v>56506</v>
+        <v>57356</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5631,22 +5648,22 @@
         <v>100</v>
       </c>
       <c r="B7" s="4">
-        <v>46909</v>
+        <v>47129</v>
       </c>
       <c r="C7" s="4">
-        <v>47818</v>
+        <v>48084</v>
       </c>
       <c r="D7" s="4">
-        <v>49473</v>
+        <v>49823</v>
       </c>
       <c r="E7" s="4">
-        <v>57452</v>
+        <v>58210</v>
       </c>
       <c r="F7" s="4">
-        <v>48349</v>
+        <v>48642</v>
       </c>
       <c r="G7" s="4">
-        <v>64812</v>
+        <v>65946</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5654,22 +5671,22 @@
         <v>101</v>
       </c>
       <c r="B8" s="4">
-        <v>50737</v>
+        <v>51011</v>
       </c>
       <c r="C8" s="4">
-        <v>51873</v>
+        <v>52205</v>
       </c>
       <c r="D8" s="4">
-        <v>53942</v>
+        <v>54380</v>
       </c>
       <c r="E8" s="4">
-        <v>63916</v>
+        <v>64864</v>
       </c>
       <c r="F8" s="4">
-        <v>52541</v>
+        <v>52908</v>
       </c>
       <c r="G8" s="4">
-        <v>73126</v>
+        <v>74543</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5677,22 +5694,22 @@
         <v>102</v>
       </c>
       <c r="B9" s="4">
-        <v>54555</v>
+        <v>54884</v>
       </c>
       <c r="C9" s="4">
-        <v>55918</v>
+        <v>56317</v>
       </c>
       <c r="D9" s="4">
-        <v>58406</v>
+        <v>58932</v>
       </c>
       <c r="E9" s="4">
-        <v>70374</v>
+        <v>71511</v>
       </c>
       <c r="F9" s="4">
-        <v>56727</v>
+        <v>57166</v>
       </c>
       <c r="G9" s="4">
-        <v>81432</v>
+        <v>83133</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5700,22 +5717,22 @@
         <v>103</v>
       </c>
       <c r="B10" s="4">
-        <v>58374</v>
+        <v>58758</v>
       </c>
       <c r="C10" s="4">
-        <v>59965</v>
+        <v>60430</v>
       </c>
       <c r="D10" s="4">
-        <v>62868</v>
+        <v>63482</v>
       </c>
       <c r="E10" s="4">
-        <v>76832</v>
+        <v>78159</v>
       </c>
       <c r="F10" s="4">
-        <v>60911</v>
+        <v>61425</v>
       </c>
       <c r="G10" s="4">
-        <v>89737</v>
+        <v>91723</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5723,22 +5740,22 @@
         <v>104</v>
       </c>
       <c r="B11" s="4">
-        <v>62192</v>
+        <v>62631</v>
       </c>
       <c r="C11" s="4">
-        <v>64010</v>
+        <v>64542</v>
       </c>
       <c r="D11" s="4">
-        <v>67332</v>
+        <v>68032</v>
       </c>
       <c r="E11" s="4">
-        <v>83289</v>
+        <v>84806</v>
       </c>
       <c r="F11" s="4">
-        <v>65097</v>
+        <v>65683</v>
       </c>
       <c r="G11" s="4">
-        <v>98044</v>
+        <v>100314</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5746,22 +5763,22 @@
         <v>105</v>
       </c>
       <c r="B12" s="4">
-        <v>66012</v>
+        <v>66506</v>
       </c>
       <c r="C12" s="4">
-        <v>68057</v>
+        <v>68655</v>
       </c>
       <c r="D12" s="4">
-        <v>71794</v>
+        <v>72583</v>
       </c>
       <c r="E12" s="4">
-        <v>89747</v>
+        <v>91454</v>
       </c>
       <c r="F12" s="4">
-        <v>69281</v>
+        <v>69942</v>
       </c>
       <c r="G12" s="4">
-        <v>106350</v>
+        <v>108903</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5769,22 +5786,22 @@
         <v>106</v>
       </c>
       <c r="B13" s="4">
-        <v>46909</v>
+        <v>47129</v>
       </c>
       <c r="C13" s="4">
-        <v>47818</v>
+        <v>48084</v>
       </c>
       <c r="D13" s="4">
-        <v>49473</v>
+        <v>49823</v>
       </c>
       <c r="E13" s="4">
-        <v>57452</v>
+        <v>58210</v>
       </c>
       <c r="F13" s="4">
-        <v>48349</v>
+        <v>48642</v>
       </c>
       <c r="G13" s="4">
-        <v>64812</v>
+        <v>65946</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5792,22 +5809,22 @@
         <v>107</v>
       </c>
       <c r="B14" s="4">
-        <v>51102</v>
+        <v>51395</v>
       </c>
       <c r="C14" s="4">
-        <v>52302</v>
+        <v>52655</v>
       </c>
       <c r="D14" s="4">
-        <v>54524</v>
+        <v>54992</v>
       </c>
       <c r="E14" s="4">
-        <v>65142</v>
+        <v>66151</v>
       </c>
       <c r="F14" s="4">
-        <v>53009</v>
+        <v>53399</v>
       </c>
       <c r="G14" s="4">
-        <v>74959</v>
+        <v>76471</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5815,22 +5832,22 @@
         <v>108</v>
       </c>
       <c r="B15" s="4">
-        <v>55274</v>
+        <v>55640</v>
       </c>
       <c r="C15" s="4">
-        <v>56776</v>
+        <v>57219</v>
       </c>
       <c r="D15" s="4">
-        <v>59567</v>
+        <v>60152</v>
       </c>
       <c r="E15" s="4">
-        <v>72823</v>
+        <v>74086</v>
       </c>
       <c r="F15" s="4">
-        <v>57661</v>
+        <v>58148</v>
       </c>
       <c r="G15" s="4">
-        <v>85098</v>
+        <v>86986</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5838,22 +5855,22 @@
         <v>109</v>
       </c>
       <c r="B16" s="4">
-        <v>59447</v>
+        <v>59886</v>
       </c>
       <c r="C16" s="4">
-        <v>61252</v>
+        <v>61783</v>
       </c>
       <c r="D16" s="4">
-        <v>64611</v>
+        <v>65313</v>
       </c>
       <c r="E16" s="4">
-        <v>80506</v>
+        <v>82021</v>
       </c>
       <c r="F16" s="4">
-        <v>62313</v>
+        <v>62898</v>
       </c>
       <c r="G16" s="4">
-        <v>95237</v>
+        <v>97503</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5861,22 +5878,22 @@
         <v>110</v>
       </c>
       <c r="B17" s="4">
-        <v>63632</v>
+        <v>64144</v>
       </c>
       <c r="C17" s="4">
-        <v>65728</v>
+        <v>66347</v>
       </c>
       <c r="D17" s="4">
-        <v>69655</v>
+        <v>70474</v>
       </c>
       <c r="E17" s="4">
-        <v>88188</v>
+        <v>89954</v>
       </c>
       <c r="F17" s="4">
-        <v>66965</v>
+        <v>67648</v>
       </c>
       <c r="G17" s="4">
-        <v>105376</v>
+        <v>108020</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5884,22 +5901,22 @@
         <v>111</v>
       </c>
       <c r="B18" s="4">
-        <v>67804</v>
+        <v>68390</v>
       </c>
       <c r="C18" s="4">
-        <v>70203</v>
+        <v>70911</v>
       </c>
       <c r="D18" s="4">
-        <v>74698</v>
+        <v>75635</v>
       </c>
       <c r="E18" s="4">
-        <v>95870</v>
+        <v>97889</v>
       </c>
       <c r="F18" s="4">
-        <v>71618</v>
+        <v>72397</v>
       </c>
       <c r="G18" s="4">
-        <v>115515</v>
+        <v>118537</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5907,22 +5924,22 @@
         <v>112</v>
       </c>
       <c r="B19" s="4">
-        <v>71977</v>
+        <v>72635</v>
       </c>
       <c r="C19" s="4">
-        <v>74679</v>
+        <v>75475</v>
       </c>
       <c r="D19" s="4">
-        <v>79741</v>
+        <v>80797</v>
       </c>
       <c r="E19" s="4">
-        <v>103553</v>
+        <v>105824</v>
       </c>
       <c r="F19" s="4">
-        <v>76270</v>
+        <v>77147</v>
       </c>
       <c r="G19" s="4">
-        <v>125655</v>
+        <v>129054</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5930,22 +5947,22 @@
         <v>113</v>
       </c>
       <c r="B20" s="4">
-        <v>50737</v>
+        <v>51011</v>
       </c>
       <c r="C20" s="4">
-        <v>51873</v>
+        <v>52205</v>
       </c>
       <c r="D20" s="4">
-        <v>53942</v>
+        <v>54380</v>
       </c>
       <c r="E20" s="4">
-        <v>63916</v>
+        <v>64864</v>
       </c>
       <c r="F20" s="4">
-        <v>52541</v>
+        <v>52908</v>
       </c>
       <c r="G20" s="4">
-        <v>73126</v>
+        <v>74543</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5953,22 +5970,22 @@
         <v>114</v>
       </c>
       <c r="B21" s="4">
-        <v>55274</v>
+        <v>55640</v>
       </c>
       <c r="C21" s="4">
-        <v>56776</v>
+        <v>57219</v>
       </c>
       <c r="D21" s="4">
-        <v>59567</v>
+        <v>60152</v>
       </c>
       <c r="E21" s="4">
-        <v>72823</v>
+        <v>74086</v>
       </c>
       <c r="F21" s="4">
-        <v>57661</v>
+        <v>58148</v>
       </c>
       <c r="G21" s="4">
-        <v>85098</v>
+        <v>86986</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5976,22 +5993,22 @@
         <v>115</v>
       </c>
       <c r="B22" s="4">
-        <v>59800</v>
+        <v>60258</v>
       </c>
       <c r="C22" s="4">
-        <v>61681</v>
+        <v>62234</v>
       </c>
       <c r="D22" s="4">
-        <v>65191</v>
+        <v>65924</v>
       </c>
       <c r="E22" s="4">
-        <v>81730</v>
+        <v>83308</v>
       </c>
       <c r="F22" s="4">
-        <v>62780</v>
+        <v>63389</v>
       </c>
       <c r="G22" s="4">
-        <v>97070</v>
+        <v>99431</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5999,22 +6016,22 @@
         <v>116</v>
       </c>
       <c r="B23" s="4">
-        <v>64339</v>
+        <v>64887</v>
       </c>
       <c r="C23" s="4">
-        <v>66586</v>
+        <v>67250</v>
       </c>
       <c r="D23" s="4">
-        <v>70815</v>
+        <v>71695</v>
       </c>
       <c r="E23" s="4">
-        <v>90764</v>
+        <v>92662</v>
       </c>
       <c r="F23" s="4">
-        <v>67900</v>
+        <v>68629</v>
       </c>
       <c r="G23" s="4">
-        <v>109042</v>
+        <v>111875</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6022,22 +6039,22 @@
         <v>117</v>
       </c>
       <c r="B24" s="4">
-        <v>68878</v>
+        <v>69517</v>
       </c>
       <c r="C24" s="4">
-        <v>71491</v>
+        <v>72264</v>
       </c>
       <c r="D24" s="4">
-        <v>76440</v>
+        <v>77467</v>
       </c>
       <c r="E24" s="4">
-        <v>99796</v>
+        <v>102016</v>
       </c>
       <c r="F24" s="4">
-        <v>73019</v>
+        <v>73870</v>
       </c>
       <c r="G24" s="4">
-        <v>121015</v>
+        <v>124318</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6045,22 +6062,22 @@
         <v>118</v>
       </c>
       <c r="B25" s="4">
-        <v>73416</v>
+        <v>74148</v>
       </c>
       <c r="C25" s="4">
-        <v>76396</v>
+        <v>77279</v>
       </c>
       <c r="D25" s="4">
-        <v>82064</v>
+        <v>83237</v>
       </c>
       <c r="E25" s="4">
-        <v>108830</v>
+        <v>111370</v>
       </c>
       <c r="F25" s="4">
-        <v>78138</v>
+        <v>79111</v>
       </c>
       <c r="G25" s="4">
-        <v>132987</v>
+        <v>136762</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6068,22 +6085,22 @@
         <v>119</v>
       </c>
       <c r="B26" s="4">
-        <v>77955</v>
+        <v>78778</v>
       </c>
       <c r="C26" s="4">
-        <v>81300</v>
+        <v>82295</v>
       </c>
       <c r="D26" s="4">
-        <v>87688</v>
+        <v>89009</v>
       </c>
       <c r="E26" s="4">
-        <v>117864</v>
+        <v>120725</v>
       </c>
       <c r="F26" s="4">
-        <v>83257</v>
+        <v>84351</v>
       </c>
       <c r="G26" s="4">
-        <v>144960</v>
+        <v>149205</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6091,22 +6108,22 @@
         <v>120</v>
       </c>
       <c r="B27" s="4">
-        <v>54555</v>
+        <v>54884</v>
       </c>
       <c r="C27" s="4">
-        <v>55918</v>
+        <v>56317</v>
       </c>
       <c r="D27" s="4">
-        <v>58406</v>
+        <v>58932</v>
       </c>
       <c r="E27" s="4">
-        <v>70374</v>
+        <v>71511</v>
       </c>
       <c r="F27" s="4">
-        <v>56727</v>
+        <v>57166</v>
       </c>
       <c r="G27" s="4">
-        <v>81432</v>
+        <v>83133</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6114,22 +6131,22 @@
         <v>121</v>
       </c>
       <c r="B28" s="4">
-        <v>59447</v>
+        <v>59886</v>
       </c>
       <c r="C28" s="4">
-        <v>61252</v>
+        <v>61783</v>
       </c>
       <c r="D28" s="4">
-        <v>64611</v>
+        <v>65313</v>
       </c>
       <c r="E28" s="4">
-        <v>80506</v>
+        <v>82021</v>
       </c>
       <c r="F28" s="4">
-        <v>62313</v>
+        <v>62898</v>
       </c>
       <c r="G28" s="4">
-        <v>95237</v>
+        <v>97503</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6137,22 +6154,22 @@
         <v>122</v>
       </c>
       <c r="B29" s="4">
-        <v>64339</v>
+        <v>64887</v>
       </c>
       <c r="C29" s="4">
-        <v>66586</v>
+        <v>67250</v>
       </c>
       <c r="D29" s="4">
-        <v>70815</v>
+        <v>71695</v>
       </c>
       <c r="E29" s="4">
-        <v>90764</v>
+        <v>92662</v>
       </c>
       <c r="F29" s="4">
-        <v>67900</v>
+        <v>68629</v>
       </c>
       <c r="G29" s="4">
-        <v>109042</v>
+        <v>111875</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6160,22 +6177,22 @@
         <v>123</v>
       </c>
       <c r="B30" s="4">
-        <v>69244</v>
+        <v>69903</v>
       </c>
       <c r="C30" s="4">
-        <v>71920</v>
+        <v>72715</v>
       </c>
       <c r="D30" s="4">
-        <v>77021</v>
+        <v>78077</v>
       </c>
       <c r="E30" s="4">
-        <v>101022</v>
+        <v>103304</v>
       </c>
       <c r="F30" s="4">
-        <v>73486</v>
+        <v>74361</v>
       </c>
       <c r="G30" s="4">
-        <v>122848</v>
+        <v>126245</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6183,22 +6200,22 @@
         <v>124</v>
       </c>
       <c r="B31" s="4">
-        <v>74135</v>
+        <v>74904</v>
       </c>
       <c r="C31" s="4">
-        <v>77255</v>
+        <v>78182</v>
       </c>
       <c r="D31" s="4">
-        <v>83226</v>
+        <v>84459</v>
       </c>
       <c r="E31" s="4">
-        <v>111279</v>
+        <v>113945</v>
       </c>
       <c r="F31" s="4">
-        <v>79073</v>
+        <v>80092</v>
       </c>
       <c r="G31" s="4">
-        <v>136654</v>
+        <v>140615</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6206,22 +6223,22 @@
         <v>125</v>
       </c>
       <c r="B32" s="4">
-        <v>79028</v>
+        <v>79906</v>
       </c>
       <c r="C32" s="4">
-        <v>82589</v>
+        <v>83648</v>
       </c>
       <c r="D32" s="4">
-        <v>89431</v>
+        <v>90841</v>
       </c>
       <c r="E32" s="4">
-        <v>121537</v>
+        <v>124587</v>
       </c>
       <c r="F32" s="4">
-        <v>84659</v>
+        <v>85824</v>
       </c>
       <c r="G32" s="4">
-        <v>150459</v>
+        <v>154985</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6229,22 +6246,22 @@
         <v>126</v>
       </c>
       <c r="B33" s="4">
-        <v>83921</v>
+        <v>84908</v>
       </c>
       <c r="C33" s="4">
-        <v>87923</v>
+        <v>89115</v>
       </c>
       <c r="D33" s="4">
-        <v>95637</v>
+        <v>97222</v>
       </c>
       <c r="E33" s="4">
-        <v>131795</v>
+        <v>135228</v>
       </c>
       <c r="F33" s="4">
-        <v>90246</v>
+        <v>91555</v>
       </c>
       <c r="G33" s="4">
-        <v>164264</v>
+        <v>169356</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6252,22 +6269,22 @@
         <v>127</v>
       </c>
       <c r="B34" s="4">
-        <v>58374</v>
+        <v>58758</v>
       </c>
       <c r="C34" s="4">
-        <v>59965</v>
+        <v>60430</v>
       </c>
       <c r="D34" s="4">
-        <v>62868</v>
+        <v>63482</v>
       </c>
       <c r="E34" s="4">
-        <v>76832</v>
+        <v>78159</v>
       </c>
       <c r="F34" s="4">
-        <v>60911</v>
+        <v>61425</v>
       </c>
       <c r="G34" s="4">
-        <v>89737</v>
+        <v>91723</v>
       </c>
     </row>
     <row r="35" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6275,22 +6292,22 @@
         <v>128</v>
       </c>
       <c r="B35" s="4">
-        <v>63632</v>
+        <v>64144</v>
       </c>
       <c r="C35" s="4">
-        <v>65728</v>
+        <v>66347</v>
       </c>
       <c r="D35" s="4">
-        <v>69655</v>
+        <v>70474</v>
       </c>
       <c r="E35" s="4">
-        <v>88188</v>
+        <v>89954</v>
       </c>
       <c r="F35" s="4">
-        <v>66965</v>
+        <v>67648</v>
       </c>
       <c r="G35" s="4">
-        <v>105376</v>
+        <v>108020</v>
       </c>
     </row>
     <row r="36" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6298,22 +6315,22 @@
         <v>129</v>
       </c>
       <c r="B36" s="4">
-        <v>74135</v>
+        <v>74904</v>
       </c>
       <c r="C36" s="4">
-        <v>77255</v>
+        <v>78182</v>
       </c>
       <c r="D36" s="4">
-        <v>83226</v>
+        <v>84459</v>
       </c>
       <c r="E36" s="4">
-        <v>111279</v>
+        <v>113945</v>
       </c>
       <c r="F36" s="4">
-        <v>79073</v>
+        <v>80092</v>
       </c>
       <c r="G36" s="4">
-        <v>136654</v>
+        <v>140615</v>
       </c>
     </row>
     <row r="37" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6321,22 +6338,22 @@
         <v>130</v>
       </c>
       <c r="B37" s="4">
-        <v>79381</v>
+        <v>80277</v>
       </c>
       <c r="C37" s="4">
-        <v>83018</v>
+        <v>84099</v>
       </c>
       <c r="D37" s="4">
-        <v>90012</v>
+        <v>91451</v>
       </c>
       <c r="E37" s="4">
-        <v>122762</v>
+        <v>125874</v>
       </c>
       <c r="F37" s="4">
-        <v>85126</v>
+        <v>86315</v>
       </c>
       <c r="G37" s="4">
-        <v>152293</v>
+        <v>156913</v>
       </c>
     </row>
     <row r="38" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6344,22 +6361,22 @@
         <v>131</v>
       </c>
       <c r="B38" s="4">
-        <v>84628</v>
+        <v>85651</v>
       </c>
       <c r="C38" s="4">
-        <v>88781</v>
+        <v>90016</v>
       </c>
       <c r="D38" s="4">
-        <v>96798</v>
+        <v>98443</v>
       </c>
       <c r="E38" s="4">
-        <v>134244</v>
+        <v>137802</v>
       </c>
       <c r="F38" s="4">
-        <v>91180</v>
+        <v>92538</v>
       </c>
       <c r="G38" s="4">
-        <v>167931</v>
+        <v>173210</v>
       </c>
     </row>
     <row r="39" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6367,22 +6384,22 @@
         <v>132</v>
       </c>
       <c r="B39" s="4">
-        <v>89872</v>
+        <v>91024</v>
       </c>
       <c r="C39" s="4">
-        <v>94544</v>
+        <v>95934</v>
       </c>
       <c r="D39" s="4">
-        <v>103584</v>
+        <v>105436</v>
       </c>
       <c r="E39" s="4">
-        <v>145727</v>
+        <v>149731</v>
       </c>
       <c r="F39" s="4">
-        <v>97233</v>
+        <v>98761</v>
       </c>
       <c r="G39" s="4">
-        <v>183569</v>
+        <v>189506</v>
       </c>
     </row>
     <row r="40" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6390,22 +6407,22 @@
         <v>133</v>
       </c>
       <c r="B40" s="4">
-        <v>62192</v>
+        <v>62631</v>
       </c>
       <c r="C40" s="4">
-        <v>64010</v>
+        <v>64542</v>
       </c>
       <c r="D40" s="4">
-        <v>67332</v>
+        <v>68032</v>
       </c>
       <c r="E40" s="4">
-        <v>83289</v>
+        <v>84806</v>
       </c>
       <c r="F40" s="4">
-        <v>65097</v>
+        <v>65683</v>
       </c>
       <c r="G40" s="4">
-        <v>98044</v>
+        <v>100314</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6413,22 +6430,22 @@
         <v>134</v>
       </c>
       <c r="B41" s="4">
-        <v>67804</v>
+        <v>68390</v>
       </c>
       <c r="C41" s="4">
-        <v>70203</v>
+        <v>70911</v>
       </c>
       <c r="D41" s="4">
-        <v>74698</v>
+        <v>75635</v>
       </c>
       <c r="E41" s="4">
-        <v>95870</v>
+        <v>97889</v>
       </c>
       <c r="F41" s="4">
-        <v>71618</v>
+        <v>72397</v>
       </c>
       <c r="G41" s="4">
-        <v>115515</v>
+        <v>118537</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6436,22 +6453,22 @@
         <v>135</v>
       </c>
       <c r="B42" s="4">
-        <v>73416</v>
+        <v>74148</v>
       </c>
       <c r="C42" s="4">
-        <v>76396</v>
+        <v>77279</v>
       </c>
       <c r="D42" s="4">
-        <v>82064</v>
+        <v>83237</v>
       </c>
       <c r="E42" s="4">
-        <v>108830</v>
+        <v>111370</v>
       </c>
       <c r="F42" s="4">
-        <v>78138</v>
+        <v>79111</v>
       </c>
       <c r="G42" s="4">
-        <v>132987</v>
+        <v>136762</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6459,22 +6476,22 @@
         <v>136</v>
       </c>
       <c r="B43" s="4">
-        <v>79028</v>
+        <v>79906</v>
       </c>
       <c r="C43" s="4">
-        <v>82589</v>
+        <v>83648</v>
       </c>
       <c r="D43" s="4">
-        <v>89431</v>
+        <v>90841</v>
       </c>
       <c r="E43" s="4">
-        <v>121537</v>
+        <v>124587</v>
       </c>
       <c r="F43" s="4">
-        <v>84659</v>
+        <v>85824</v>
       </c>
       <c r="G43" s="4">
-        <v>150459</v>
+        <v>154985</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6482,22 +6499,22 @@
         <v>137</v>
       </c>
       <c r="B44" s="4">
-        <v>84628</v>
+        <v>85651</v>
       </c>
       <c r="C44" s="4">
-        <v>88781</v>
+        <v>90016</v>
       </c>
       <c r="D44" s="4">
-        <v>96798</v>
+        <v>98443</v>
       </c>
       <c r="E44" s="4">
-        <v>134244</v>
+        <v>137802</v>
       </c>
       <c r="F44" s="4">
-        <v>91180</v>
+        <v>92538</v>
       </c>
       <c r="G44" s="4">
-        <v>167931</v>
+        <v>173210</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6505,22 +6522,22 @@
         <v>138</v>
       </c>
       <c r="B45" s="4">
-        <v>90239</v>
+        <v>91409</v>
       </c>
       <c r="C45" s="4">
-        <v>94973</v>
+        <v>96385</v>
       </c>
       <c r="D45" s="4">
-        <v>104164</v>
+        <v>106046</v>
       </c>
       <c r="E45" s="4">
-        <v>146951</v>
+        <v>151018</v>
       </c>
       <c r="F45" s="4">
-        <v>97700</v>
+        <v>99252</v>
       </c>
       <c r="G45" s="4">
-        <v>185402</v>
+        <v>191434</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6528,22 +6545,22 @@
         <v>139</v>
       </c>
       <c r="B46" s="4">
-        <v>95858</v>
+        <v>97175</v>
       </c>
       <c r="C46" s="4">
-        <v>101173</v>
+        <v>102760</v>
       </c>
       <c r="D46" s="4">
-        <v>111526</v>
+        <v>113642</v>
       </c>
       <c r="E46" s="4">
-        <v>159666</v>
+        <v>164242</v>
       </c>
       <c r="F46" s="4">
-        <v>104229</v>
+        <v>105973</v>
       </c>
       <c r="G46" s="4">
-        <v>202882</v>
+        <v>209666</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6551,22 +6568,22 @@
         <v>140</v>
       </c>
       <c r="B47" s="4">
-        <v>66012</v>
+        <v>66506</v>
       </c>
       <c r="C47" s="4">
-        <v>68057</v>
+        <v>68655</v>
       </c>
       <c r="D47" s="4">
-        <v>71794</v>
+        <v>72583</v>
       </c>
       <c r="E47" s="4">
-        <v>89747</v>
+        <v>91454</v>
       </c>
       <c r="F47" s="4">
-        <v>69281</v>
+        <v>69942</v>
       </c>
       <c r="G47" s="4">
-        <v>106350</v>
+        <v>108903</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6574,22 +6591,22 @@
         <v>141</v>
       </c>
       <c r="B48" s="4">
-        <v>71977</v>
+        <v>72635</v>
       </c>
       <c r="C48" s="4">
-        <v>74679</v>
+        <v>75475</v>
       </c>
       <c r="D48" s="4">
-        <v>79741</v>
+        <v>80797</v>
       </c>
       <c r="E48" s="4">
-        <v>103553</v>
+        <v>105824</v>
       </c>
       <c r="F48" s="4">
-        <v>76270</v>
+        <v>77147</v>
       </c>
       <c r="G48" s="4">
-        <v>125655</v>
+        <v>129054</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6597,22 +6614,22 @@
         <v>142</v>
       </c>
       <c r="B49" s="4">
-        <v>77955</v>
+        <v>78778</v>
       </c>
       <c r="C49" s="4">
-        <v>81300</v>
+        <v>82295</v>
       </c>
       <c r="D49" s="4">
-        <v>87688</v>
+        <v>89009</v>
       </c>
       <c r="E49" s="4">
-        <v>117864</v>
+        <v>120725</v>
       </c>
       <c r="F49" s="4">
-        <v>83257</v>
+        <v>84351</v>
       </c>
       <c r="G49" s="4">
-        <v>144960</v>
+        <v>149205</v>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6620,22 +6637,22 @@
         <v>143</v>
       </c>
       <c r="B50" s="4">
-        <v>83921</v>
+        <v>84908</v>
       </c>
       <c r="C50" s="4">
-        <v>87923</v>
+        <v>89115</v>
       </c>
       <c r="D50" s="4">
-        <v>95637</v>
+        <v>97222</v>
       </c>
       <c r="E50" s="4">
-        <v>131795</v>
+        <v>135228</v>
       </c>
       <c r="F50" s="4">
-        <v>90246</v>
+        <v>91555</v>
       </c>
       <c r="G50" s="4">
-        <v>164264</v>
+        <v>169356</v>
       </c>
     </row>
     <row r="51" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6643,22 +6660,22 @@
         <v>144</v>
       </c>
       <c r="B51" s="4">
-        <v>89872</v>
+        <v>91024</v>
       </c>
       <c r="C51" s="4">
-        <v>94544</v>
+        <v>95934</v>
       </c>
       <c r="D51" s="4">
-        <v>103584</v>
+        <v>105436</v>
       </c>
       <c r="E51" s="4">
-        <v>145727</v>
+        <v>149731</v>
       </c>
       <c r="F51" s="4">
-        <v>97233</v>
+        <v>98761</v>
       </c>
       <c r="G51" s="4">
-        <v>183569</v>
+        <v>189506</v>
       </c>
     </row>
     <row r="52" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6666,22 +6683,22 @@
         <v>145</v>
       </c>
       <c r="B52" s="4">
-        <v>95858</v>
+        <v>97175</v>
       </c>
       <c r="C52" s="4">
-        <v>101173</v>
+        <v>102760</v>
       </c>
       <c r="D52" s="4">
-        <v>111526</v>
+        <v>113642</v>
       </c>
       <c r="E52" s="4">
-        <v>159666</v>
+        <v>164242</v>
       </c>
       <c r="F52" s="4">
-        <v>104229</v>
+        <v>105973</v>
       </c>
       <c r="G52" s="4">
-        <v>202882</v>
+        <v>209666</v>
       </c>
     </row>
     <row r="53" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6689,22 +6706,22 @@
         <v>25</v>
       </c>
       <c r="B53" s="4">
-        <v>101835</v>
+        <v>103317</v>
       </c>
       <c r="C53" s="4">
-        <v>107138</v>
+        <v>108891</v>
       </c>
       <c r="D53" s="4">
-        <v>119461</v>
+        <v>121842</v>
       </c>
       <c r="E53" s="4">
-        <v>172929</v>
+        <v>178042</v>
       </c>
       <c r="F53" s="4">
-        <v>111216</v>
+        <v>113177</v>
       </c>
       <c r="G53" s="4">
-        <v>222187</v>
+        <v>229817</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6712,22 +6729,22 @@
         <v>146</v>
       </c>
       <c r="B54" s="4">
-        <v>69831</v>
+        <v>70379</v>
       </c>
       <c r="C54" s="4">
-        <v>72103</v>
+        <v>72767</v>
       </c>
       <c r="D54" s="4">
-        <v>76270</v>
+        <v>77147</v>
       </c>
       <c r="E54" s="4">
-        <v>96166</v>
+        <v>98060</v>
       </c>
       <c r="F54" s="4">
-        <v>73416</v>
+        <v>74148</v>
       </c>
       <c r="G54" s="4">
-        <v>114565</v>
+        <v>117397</v>
       </c>
     </row>
     <row r="55" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6735,22 +6752,22 @@
         <v>147</v>
       </c>
       <c r="B55" s="4">
-        <v>76162</v>
+        <v>76894</v>
       </c>
       <c r="C55" s="4">
-        <v>79179</v>
+        <v>80065</v>
       </c>
       <c r="D55" s="4">
-        <v>84734</v>
+        <v>85904</v>
       </c>
       <c r="E55" s="4">
-        <v>111273</v>
+        <v>113798</v>
       </c>
       <c r="F55" s="4">
-        <v>80934</v>
+        <v>81909</v>
       </c>
       <c r="G55" s="4">
-        <v>135809</v>
+        <v>139587</v>
       </c>
     </row>
     <row r="56" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6758,22 +6775,22 @@
         <v>148</v>
       </c>
       <c r="B56" s="4">
-        <v>82493</v>
+        <v>83408</v>
       </c>
       <c r="C56" s="4">
-        <v>86268</v>
+        <v>87376</v>
       </c>
       <c r="D56" s="4">
-        <v>93200</v>
+        <v>94661</v>
       </c>
       <c r="E56" s="4">
-        <v>126379</v>
+        <v>129535</v>
       </c>
       <c r="F56" s="4">
-        <v>88452</v>
+        <v>89671</v>
       </c>
       <c r="G56" s="4">
-        <v>157053</v>
+        <v>161777</v>
       </c>
     </row>
     <row r="57" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6781,22 +6798,22 @@
         <v>149</v>
       </c>
       <c r="B57" s="4">
-        <v>88824</v>
+        <v>89922</v>
       </c>
       <c r="C57" s="4">
-        <v>93345</v>
+        <v>94673</v>
       </c>
       <c r="D57" s="4">
-        <v>101664</v>
+        <v>103418</v>
       </c>
       <c r="E57" s="4">
-        <v>141484</v>
+        <v>145272</v>
       </c>
       <c r="F57" s="4">
-        <v>95970</v>
+        <v>97434</v>
       </c>
       <c r="G57" s="4">
-        <v>178297</v>
+        <v>183965</v>
       </c>
     </row>
     <row r="58" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6804,22 +6821,22 @@
         <v>150</v>
       </c>
       <c r="B58" s="4">
-        <v>95163</v>
+        <v>96444</v>
       </c>
       <c r="C58" s="4">
-        <v>100429</v>
+        <v>101978</v>
       </c>
       <c r="D58" s="4">
-        <v>110137</v>
+        <v>112182</v>
       </c>
       <c r="E58" s="4">
-        <v>156598</v>
+        <v>161016</v>
       </c>
       <c r="F58" s="4">
-        <v>103496</v>
+        <v>105202</v>
       </c>
       <c r="G58" s="4">
-        <v>199549</v>
+        <v>206162</v>
       </c>
     </row>
     <row r="59" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6827,22 +6844,22 @@
         <v>151</v>
       </c>
       <c r="B59" s="4">
-        <v>101495</v>
+        <v>102959</v>
       </c>
       <c r="C59" s="4">
-        <v>107504</v>
+        <v>109275</v>
       </c>
       <c r="D59" s="4">
-        <v>118603</v>
+        <v>120941</v>
       </c>
       <c r="E59" s="4">
-        <v>171704</v>
+        <v>176755</v>
       </c>
       <c r="F59" s="4">
-        <v>111014</v>
+        <v>112965</v>
       </c>
       <c r="G59" s="4">
-        <v>220793</v>
+        <v>228351</v>
       </c>
     </row>
     <row r="60" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6850,22 +6867,22 @@
         <v>32</v>
       </c>
       <c r="B60" s="4">
-        <v>107827</v>
+        <v>109474</v>
       </c>
       <c r="C60" s="4">
-        <v>114581</v>
+        <v>116573</v>
       </c>
       <c r="D60" s="4">
-        <v>127067</v>
+        <v>129698</v>
       </c>
       <c r="E60" s="4">
-        <v>186810</v>
+        <v>192491</v>
       </c>
       <c r="F60" s="4">
-        <v>118532</v>
+        <v>120726</v>
       </c>
       <c r="G60" s="4">
-        <v>242037</v>
+        <v>250540</v>
       </c>
     </row>
     <row r="61" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6873,22 +6890,22 @@
         <v>152</v>
       </c>
       <c r="B61" s="4">
-        <v>73662</v>
+        <v>74266</v>
       </c>
       <c r="C61" s="4">
-        <v>76150</v>
+        <v>76880</v>
       </c>
       <c r="D61" s="4">
-        <v>80732</v>
+        <v>81697</v>
       </c>
       <c r="E61" s="4">
-        <v>102624</v>
+        <v>104708</v>
       </c>
       <c r="F61" s="4">
-        <v>77588</v>
+        <v>78393</v>
       </c>
       <c r="G61" s="4">
-        <v>122855</v>
+        <v>125972</v>
       </c>
     </row>
     <row r="62" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6896,22 +6913,22 @@
         <v>153</v>
       </c>
       <c r="B62" s="4">
-        <v>80348</v>
+        <v>81152</v>
       </c>
       <c r="C62" s="4">
-        <v>83668</v>
+        <v>84642</v>
       </c>
       <c r="D62" s="4">
-        <v>89778</v>
+        <v>91065</v>
       </c>
       <c r="E62" s="4">
-        <v>118967</v>
+        <v>121745</v>
       </c>
       <c r="F62" s="4">
-        <v>85586</v>
+        <v>86659</v>
       </c>
       <c r="G62" s="4">
-        <v>145948</v>
+        <v>150104</v>
       </c>
     </row>
     <row r="63" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6919,22 +6936,22 @@
         <v>154</v>
       </c>
       <c r="B63" s="4">
-        <v>87032</v>
+        <v>88038</v>
       </c>
       <c r="C63" s="4">
-        <v>91186</v>
+        <v>92404</v>
       </c>
       <c r="D63" s="4">
-        <v>98824</v>
+        <v>100433</v>
       </c>
       <c r="E63" s="4">
-        <v>135311</v>
+        <v>138783</v>
       </c>
       <c r="F63" s="4">
-        <v>93584</v>
+        <v>94925</v>
       </c>
       <c r="G63" s="4">
-        <v>169041</v>
+        <v>174236</v>
       </c>
     </row>
     <row r="64" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6942,22 +6959,22 @@
         <v>155</v>
       </c>
       <c r="B64" s="4">
-        <v>93724</v>
+        <v>94931</v>
       </c>
       <c r="C64" s="4">
-        <v>98711</v>
+        <v>100173</v>
       </c>
       <c r="D64" s="4">
-        <v>107878</v>
+        <v>109807</v>
       </c>
       <c r="E64" s="4">
-        <v>151662</v>
+        <v>155829</v>
       </c>
       <c r="F64" s="4">
-        <v>101590</v>
+        <v>103200</v>
       </c>
       <c r="G64" s="4">
-        <v>192140</v>
+        <v>198375</v>
       </c>
     </row>
     <row r="65" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6965,22 +6982,22 @@
         <v>156</v>
       </c>
       <c r="B65" s="4">
-        <v>100409</v>
+        <v>101818</v>
       </c>
       <c r="C65" s="4">
-        <v>106229</v>
+        <v>107936</v>
       </c>
       <c r="D65" s="4">
-        <v>116924</v>
+        <v>119175</v>
       </c>
       <c r="E65" s="4">
-        <v>168005</v>
+        <v>172867</v>
       </c>
       <c r="F65" s="4">
-        <v>109588</v>
+        <v>111465</v>
       </c>
       <c r="G65" s="4">
-        <v>215233</v>
+        <v>222507</v>
       </c>
     </row>
     <row r="66" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6988,22 +7005,22 @@
         <v>157</v>
       </c>
       <c r="B66" s="4">
-        <v>107094</v>
+        <v>108704</v>
       </c>
       <c r="C66" s="4">
-        <v>113747</v>
+        <v>115697</v>
       </c>
       <c r="D66" s="4">
-        <v>125968</v>
+        <v>128543</v>
       </c>
       <c r="E66" s="4">
-        <v>184348</v>
+        <v>189904</v>
       </c>
       <c r="F66" s="4">
-        <v>117586</v>
+        <v>119731</v>
       </c>
       <c r="G66" s="4">
-        <v>238326</v>
+        <v>246639</v>
       </c>
     </row>
     <row r="67" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7011,22 +7028,22 @@
         <v>38</v>
       </c>
       <c r="B67" s="4">
-        <v>113780</v>
+        <v>115592</v>
       </c>
       <c r="C67" s="4">
-        <v>121267</v>
+        <v>123461</v>
       </c>
       <c r="D67" s="4">
-        <v>135016</v>
+        <v>137911</v>
       </c>
       <c r="E67" s="4">
-        <v>200693</v>
+        <v>206942</v>
       </c>
       <c r="F67" s="4">
-        <v>125585</v>
+        <v>127999</v>
       </c>
       <c r="G67" s="4">
-        <v>261419</v>
+        <v>270772</v>
       </c>
     </row>
     <row r="68" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7034,22 +7051,22 @@
         <v>158</v>
       </c>
       <c r="B68" s="4">
-        <v>85126</v>
+        <v>85895</v>
       </c>
       <c r="C68" s="4">
-        <v>88296</v>
+        <v>89225</v>
       </c>
       <c r="D68" s="4">
-        <v>94129</v>
+        <v>95356</v>
       </c>
       <c r="E68" s="4">
-        <v>121992</v>
+        <v>124644</v>
       </c>
       <c r="F68" s="4">
-        <v>90139</v>
+        <v>91163</v>
       </c>
       <c r="G68" s="4">
-        <v>147750</v>
+        <v>151717</v>
       </c>
     </row>
     <row r="69" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7057,22 +7074,22 @@
         <v>159</v>
       </c>
       <c r="B69" s="4">
-        <v>92885</v>
+        <v>93909</v>
       </c>
       <c r="C69" s="4">
-        <v>97114</v>
+        <v>98354</v>
       </c>
       <c r="D69" s="4">
-        <v>104891</v>
+        <v>106528</v>
       </c>
       <c r="E69" s="4">
-        <v>142035</v>
+        <v>145570</v>
       </c>
       <c r="F69" s="4">
-        <v>99563</v>
+        <v>100929</v>
       </c>
       <c r="G69" s="4">
-        <v>176373</v>
+        <v>181662</v>
       </c>
     </row>
     <row r="70" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7080,22 +7097,22 @@
         <v>160</v>
       </c>
       <c r="B70" s="4">
-        <v>100642</v>
+        <v>101923</v>
       </c>
       <c r="C70" s="4">
-        <v>105933</v>
+        <v>107483</v>
       </c>
       <c r="D70" s="4">
-        <v>115654</v>
+        <v>117701</v>
       </c>
       <c r="E70" s="4">
-        <v>162077</v>
+        <v>166496</v>
       </c>
       <c r="F70" s="4">
-        <v>108988</v>
+        <v>110694</v>
       </c>
       <c r="G70" s="4">
-        <v>204995</v>
+        <v>211605</v>
       </c>
     </row>
     <row r="71" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7103,22 +7120,22 @@
         <v>161</v>
       </c>
       <c r="B71" s="4">
-        <v>108402</v>
+        <v>109938</v>
       </c>
       <c r="C71" s="4">
-        <v>114752</v>
+        <v>116614</v>
       </c>
       <c r="D71" s="4">
-        <v>126419</v>
+        <v>128874</v>
       </c>
       <c r="E71" s="4">
-        <v>182121</v>
+        <v>187423</v>
       </c>
       <c r="F71" s="4">
-        <v>118414</v>
+        <v>120462</v>
       </c>
       <c r="G71" s="4">
-        <v>233619</v>
+        <v>241551</v>
       </c>
     </row>
     <row r="72" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7126,22 +7143,22 @@
         <v>162</v>
       </c>
       <c r="B72" s="4">
-        <v>116160</v>
+        <v>117952</v>
       </c>
       <c r="C72" s="4">
-        <v>123571</v>
+        <v>125741</v>
       </c>
       <c r="D72" s="4">
-        <v>137181</v>
+        <v>140047</v>
       </c>
       <c r="E72" s="4">
-        <v>202163</v>
+        <v>208349</v>
       </c>
       <c r="F72" s="4">
-        <v>127839</v>
+        <v>130227</v>
       </c>
       <c r="G72" s="4">
-        <v>252697</v>
+        <v>261464</v>
       </c>
     </row>
     <row r="73" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7149,22 +7166,22 @@
         <v>163</v>
       </c>
       <c r="B73" s="4">
-        <v>123918</v>
+        <v>125966</v>
       </c>
       <c r="C73" s="4">
-        <v>132389</v>
+        <v>134871</v>
       </c>
       <c r="D73" s="4">
-        <v>147943</v>
+        <v>151219</v>
       </c>
       <c r="E73" s="4">
-        <v>222205</v>
+        <v>229275</v>
       </c>
       <c r="F73" s="4">
-        <v>137263</v>
+        <v>139993</v>
       </c>
       <c r="G73" s="4">
-        <v>271775</v>
+        <v>281375</v>
       </c>
     </row>
     <row r="74" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7172,22 +7189,22 @@
         <v>45</v>
       </c>
       <c r="B74" s="4">
-        <v>131676</v>
+        <v>133980</v>
       </c>
       <c r="C74" s="4">
-        <v>141208</v>
+        <v>144000</v>
       </c>
       <c r="D74" s="4">
-        <v>158707</v>
+        <v>162392</v>
       </c>
       <c r="E74" s="4">
-        <v>242248</v>
+        <v>250200</v>
       </c>
       <c r="F74" s="4">
-        <v>146687</v>
+        <v>149758</v>
       </c>
       <c r="G74" s="4">
-        <v>300398</v>
+        <v>311320</v>
       </c>
     </row>
   </sheetData>
@@ -7260,19 +7277,19 @@
         <v>169</v>
       </c>
       <c r="C6" s="4">
-        <v>188936</v>
+        <v>190684</v>
       </c>
       <c r="D6" s="4">
-        <v>199541</v>
+        <v>201843</v>
       </c>
       <c r="E6" s="4">
-        <v>192303</v>
+        <v>194226</v>
       </c>
       <c r="F6" s="4">
-        <v>250819</v>
+        <v>255800</v>
       </c>
       <c r="G6" s="4">
-        <v>298147</v>
+        <v>305600</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7283,16 +7300,16 @@
         <v>169</v>
       </c>
       <c r="C7" s="4">
-        <v>239521</v>
+        <v>241270</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>169</v>
       </c>
       <c r="E7" s="4">
-        <v>242888</v>
+        <v>244812</v>
       </c>
       <c r="F7" s="4">
-        <v>301405</v>
+        <v>306385</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>169</v>
@@ -7303,19 +7320,19 @@
         <v>171</v>
       </c>
       <c r="B8" s="4">
-        <v>190028</v>
+        <v>191395</v>
       </c>
       <c r="C8" s="4">
-        <v>195583</v>
+        <v>197240</v>
       </c>
       <c r="D8" s="4">
-        <v>205615</v>
+        <v>207796</v>
       </c>
       <c r="E8" s="4">
-        <v>198762</v>
+        <v>200585</v>
       </c>
       <c r="F8" s="4">
-        <v>254201</v>
+        <v>258922</v>
       </c>
       <c r="G8" s="4">
         <v>266860</v>
@@ -7326,19 +7343,19 @@
         <v>172</v>
       </c>
       <c r="B9" s="4">
-        <v>229882</v>
+        <v>230566</v>
       </c>
       <c r="C9" s="4">
-        <v>232659</v>
+        <v>233487</v>
       </c>
       <c r="D9" s="4">
-        <v>237674</v>
+        <v>238766</v>
       </c>
       <c r="E9" s="4">
-        <v>234248</v>
+        <v>235159</v>
       </c>
       <c r="F9" s="4">
-        <v>261969</v>
+        <v>264328</v>
       </c>
       <c r="G9" s="4">
         <v>268297</v>
@@ -7349,7 +7366,7 @@
         <v>173</v>
       </c>
       <c r="B10" s="4">
-        <v>261226</v>
+        <v>261909</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>169</v>
@@ -7358,10 +7375,10 @@
         <v>169</v>
       </c>
       <c r="E10" s="4">
-        <v>265591</v>
+        <v>266503</v>
       </c>
       <c r="F10" s="4">
-        <v>293312</v>
+        <v>295671</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>169</v>
@@ -7372,19 +7389,19 @@
         <v>174</v>
       </c>
       <c r="B11" s="4">
-        <v>250579</v>
+        <v>250961</v>
       </c>
       <c r="C11" s="4">
-        <v>252074</v>
+        <v>252534</v>
       </c>
       <c r="D11" s="4">
-        <v>254869</v>
+        <v>255474</v>
       </c>
       <c r="E11" s="4">
-        <v>252962</v>
+        <v>253470</v>
       </c>
       <c r="F11" s="4">
-        <v>268361</v>
+        <v>269672</v>
       </c>
       <c r="G11" s="4">
         <v>271877</v>
@@ -7395,7 +7412,7 @@
         <v>175</v>
       </c>
       <c r="B12" s="4">
-        <v>271400</v>
+        <v>271782</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>169</v>
@@ -7404,10 +7421,10 @@
         <v>169</v>
       </c>
       <c r="E12" s="4">
-        <v>273784</v>
+        <v>274291</v>
       </c>
       <c r="F12" s="4">
-        <v>289182</v>
+        <v>290493</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>169</v>
@@ -7441,19 +7458,19 @@
         <v>177</v>
       </c>
       <c r="B14" s="4">
-        <v>254954</v>
+        <v>255637</v>
       </c>
       <c r="C14" s="4">
-        <v>257731</v>
+        <v>258559</v>
       </c>
       <c r="D14" s="4">
-        <v>262746</v>
+        <v>263838</v>
       </c>
       <c r="E14" s="4">
-        <v>259320</v>
+        <v>260231</v>
       </c>
       <c r="F14" s="4">
-        <v>287041</v>
+        <v>289399</v>
       </c>
       <c r="G14" s="4">
         <v>293369</v>
@@ -7464,19 +7481,19 @@
         <v>178</v>
       </c>
       <c r="B15" s="4">
-        <v>263113</v>
+        <v>263495</v>
       </c>
       <c r="C15" s="4">
-        <v>264609</v>
+        <v>265069</v>
       </c>
       <c r="D15" s="4">
-        <v>267403</v>
+        <v>268008</v>
       </c>
       <c r="E15" s="4">
-        <v>265497</v>
+        <v>266004</v>
       </c>
       <c r="F15" s="4">
-        <v>280895</v>
+        <v>282206</v>
       </c>
       <c r="G15" s="4">
         <v>284411</v>
@@ -7487,19 +7504,19 @@
         <v>179</v>
       </c>
       <c r="B16" s="4">
-        <v>212605</v>
+        <v>214132</v>
       </c>
       <c r="C16" s="4">
-        <v>218586</v>
+        <v>220426</v>
       </c>
       <c r="D16" s="4">
-        <v>229763</v>
+        <v>232187</v>
       </c>
       <c r="E16" s="4">
-        <v>222141</v>
+        <v>224166</v>
       </c>
       <c r="F16" s="4">
-        <v>283733</v>
+        <v>288977</v>
       </c>
       <c r="G16" s="4">
         <v>297798</v>
@@ -7510,19 +7527,19 @@
         <v>180</v>
       </c>
       <c r="B17" s="4">
-        <v>256654</v>
+        <v>257134</v>
       </c>
       <c r="C17" s="4">
-        <v>258602</v>
+        <v>259184</v>
       </c>
       <c r="D17" s="4">
-        <v>262140</v>
+        <v>262908</v>
       </c>
       <c r="E17" s="4">
-        <v>259756</v>
+        <v>260399</v>
       </c>
       <c r="F17" s="4">
-        <v>279238</v>
+        <v>280899</v>
       </c>
       <c r="G17" s="4">
         <v>283688</v>
@@ -7533,19 +7550,19 @@
         <v>181</v>
       </c>
       <c r="B18" s="4">
-        <v>267856</v>
+        <v>268121</v>
       </c>
       <c r="C18" s="4">
-        <v>269812</v>
+        <v>270180</v>
       </c>
       <c r="D18" s="4">
-        <v>272043</v>
+        <v>272527</v>
       </c>
       <c r="E18" s="4">
-        <v>270521</v>
+        <v>270927</v>
       </c>
       <c r="F18" s="4">
-        <v>282844</v>
+        <v>283892</v>
       </c>
       <c r="G18" s="4">
         <v>285648</v>
@@ -7556,7 +7573,7 @@
         <v>182</v>
       </c>
       <c r="B19" s="4">
-        <v>288396</v>
+        <v>288662</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>169</v>
@@ -7565,10 +7582,10 @@
         <v>169</v>
       </c>
       <c r="E19" s="4">
-        <v>291061</v>
+        <v>291467</v>
       </c>
       <c r="F19" s="4">
-        <v>303384</v>
+        <v>304432</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>169</v>
@@ -7579,19 +7596,19 @@
         <v>183</v>
       </c>
       <c r="B20" s="4">
-        <v>249688</v>
+        <v>250751</v>
       </c>
       <c r="C20" s="4">
-        <v>255747</v>
+        <v>257127</v>
       </c>
       <c r="D20" s="4">
-        <v>264120</v>
+        <v>265939</v>
       </c>
       <c r="E20" s="4">
-        <v>258413</v>
+        <v>259932</v>
       </c>
       <c r="F20" s="4">
-        <v>304615</v>
+        <v>308548</v>
       </c>
       <c r="G20" s="4">
         <v>315163</v>
@@ -7602,19 +7619,19 @@
         <v>184</v>
       </c>
       <c r="B21" s="4">
-        <v>210690</v>
+        <v>211753</v>
       </c>
       <c r="C21" s="4">
-        <v>216749</v>
+        <v>218129</v>
       </c>
       <c r="D21" s="4">
-        <v>225122</v>
+        <v>226940</v>
       </c>
       <c r="E21" s="4">
-        <v>219415</v>
+        <v>220934</v>
       </c>
       <c r="F21" s="4">
-        <v>265617</v>
+        <v>269550</v>
       </c>
       <c r="G21" s="4">
         <v>276165</v>
@@ -7702,16 +7719,16 @@
         <v>190</v>
       </c>
       <c r="B6" s="4">
-        <v>149825</v>
+        <v>150958</v>
       </c>
       <c r="C6" s="4">
-        <v>223012</v>
+        <v>227856</v>
       </c>
       <c r="D6" s="4">
-        <v>152076</v>
+        <v>153322</v>
       </c>
       <c r="E6" s="4">
-        <v>191148</v>
+        <v>194378</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7719,16 +7736,16 @@
         <v>191</v>
       </c>
       <c r="B7" s="4">
-        <v>168244</v>
+        <v>169378</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>169</v>
       </c>
       <c r="D7" s="4">
-        <v>170495</v>
+        <v>171742</v>
       </c>
       <c r="E7" s="4">
-        <v>209568</v>
+        <v>212797</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7736,16 +7753,16 @@
         <v>192</v>
       </c>
       <c r="B8" s="4">
-        <v>176258</v>
+        <v>177153</v>
       </c>
       <c r="C8" s="4">
-        <v>234044</v>
+        <v>237870</v>
       </c>
       <c r="D8" s="4">
-        <v>178038</v>
+        <v>179023</v>
       </c>
       <c r="E8" s="4">
-        <v>208888</v>
+        <v>211437</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7753,16 +7770,16 @@
         <v>193</v>
       </c>
       <c r="B9" s="4">
-        <v>194816</v>
+        <v>195710</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>169</v>
       </c>
       <c r="D9" s="4">
-        <v>196595</v>
+        <v>197580</v>
       </c>
       <c r="E9" s="4">
-        <v>227445</v>
+        <v>229994</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7770,16 +7787,16 @@
         <v>194</v>
       </c>
       <c r="B10" s="4">
-        <v>204190</v>
+        <v>204787</v>
       </c>
       <c r="C10" s="4">
-        <v>242708</v>
+        <v>245258</v>
       </c>
       <c r="D10" s="4">
-        <v>205371</v>
+        <v>206027</v>
       </c>
       <c r="E10" s="4">
-        <v>225935</v>
+        <v>227634</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7787,16 +7804,16 @@
         <v>195</v>
       </c>
       <c r="B11" s="4">
-        <v>214258</v>
+        <v>214855</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>169</v>
       </c>
       <c r="D11" s="4">
-        <v>215439</v>
+        <v>216095</v>
       </c>
       <c r="E11" s="4">
-        <v>236003</v>
+        <v>237702</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7804,16 +7821,16 @@
         <v>196</v>
       </c>
       <c r="B12" s="4">
-        <v>182648</v>
+        <v>184139</v>
       </c>
       <c r="C12" s="4">
-        <v>278952</v>
+        <v>285328</v>
       </c>
       <c r="D12" s="4">
-        <v>185608</v>
+        <v>187249</v>
       </c>
       <c r="E12" s="4">
-        <v>237021</v>
+        <v>241270</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7821,16 +7838,16 @@
         <v>197</v>
       </c>
       <c r="B13" s="4">
-        <v>166807</v>
+        <v>181069</v>
       </c>
       <c r="C13" s="4">
-        <v>223236</v>
+        <v>236878</v>
       </c>
       <c r="D13" s="4">
-        <v>166187</v>
+        <v>179829</v>
       </c>
       <c r="E13" s="4">
-        <v>203393</v>
+        <v>218275</v>
       </c>
     </row>
   </sheetData>
@@ -7905,25 +7922,25 @@
         <v>6</v>
       </c>
       <c r="B6" s="4">
-        <v>104834</v>
+        <v>108088</v>
       </c>
       <c r="C6" s="4">
-        <v>105559</v>
+        <v>108851</v>
       </c>
       <c r="D6" s="4">
-        <v>106888</v>
+        <v>110247</v>
       </c>
       <c r="E6" s="4">
-        <v>118664</v>
+        <v>122615</v>
       </c>
       <c r="F6" s="4">
         <v>9200</v>
       </c>
       <c r="G6" s="4">
-        <v>15615</v>
+        <v>16090</v>
       </c>
       <c r="H6" s="4">
-        <v>156043</v>
+        <v>159547</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7931,25 +7948,25 @@
         <v>7</v>
       </c>
       <c r="B7" s="4">
-        <v>115902</v>
+        <v>119520</v>
       </c>
       <c r="C7" s="4">
-        <v>116930</v>
+        <v>120602</v>
       </c>
       <c r="D7" s="4">
-        <v>118796</v>
+        <v>122563</v>
       </c>
       <c r="E7" s="4">
-        <v>135286</v>
+        <v>139881</v>
       </c>
       <c r="F7" s="4">
         <v>9200</v>
       </c>
       <c r="G7" s="4">
-        <v>18296</v>
+        <v>18853</v>
       </c>
       <c r="H7" s="4">
-        <v>175707</v>
+        <v>179673</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7957,25 +7974,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="4">
-        <v>128486</v>
+        <v>132511</v>
       </c>
       <c r="C8" s="4">
-        <v>129815</v>
+        <v>133912</v>
       </c>
       <c r="D8" s="4">
-        <v>132204</v>
+        <v>136420</v>
       </c>
       <c r="E8" s="4">
-        <v>153404</v>
+        <v>158688</v>
       </c>
       <c r="F8" s="4">
         <v>9200</v>
       </c>
       <c r="G8" s="4">
-        <v>20978</v>
+        <v>21615</v>
       </c>
       <c r="H8" s="4">
-        <v>196889</v>
+        <v>201367</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7983,25 +8000,25 @@
         <v>9</v>
       </c>
       <c r="B9" s="4">
-        <v>141094</v>
+        <v>145528</v>
       </c>
       <c r="C9" s="4">
-        <v>142699</v>
+        <v>147221</v>
       </c>
       <c r="D9" s="4">
-        <v>145625</v>
+        <v>150294</v>
       </c>
       <c r="E9" s="4">
-        <v>171532</v>
+        <v>177502</v>
       </c>
       <c r="F9" s="4">
         <v>9200</v>
       </c>
       <c r="G9" s="4">
-        <v>23659</v>
+        <v>24378</v>
       </c>
       <c r="H9" s="4">
-        <v>218066</v>
+        <v>223052</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8009,25 +8026,25 @@
         <v>10</v>
       </c>
       <c r="B10" s="4">
-        <v>162226</v>
+        <v>167343</v>
       </c>
       <c r="C10" s="4">
-        <v>164281</v>
+        <v>169509</v>
       </c>
       <c r="D10" s="4">
-        <v>168006</v>
+        <v>173421</v>
       </c>
       <c r="E10" s="4">
-        <v>200983</v>
+        <v>208058</v>
       </c>
       <c r="F10" s="4">
         <v>9200</v>
       </c>
       <c r="G10" s="4">
-        <v>27681</v>
+        <v>28524</v>
       </c>
       <c r="H10" s="4">
-        <v>252076</v>
+        <v>257897</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8035,25 +8052,25 @@
         <v>11</v>
       </c>
       <c r="B11" s="4">
-        <v>184042</v>
+        <v>189861</v>
       </c>
       <c r="C11" s="4">
-        <v>186527</v>
+        <v>192482</v>
       </c>
       <c r="D11" s="4">
-        <v>191051</v>
+        <v>197233</v>
       </c>
       <c r="E11" s="4">
-        <v>231101</v>
+        <v>239299</v>
       </c>
       <c r="F11" s="4">
         <v>9200</v>
       </c>
       <c r="G11" s="4">
-        <v>31703</v>
+        <v>32667</v>
       </c>
       <c r="H11" s="4">
-        <v>286759</v>
+        <v>293433</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8061,25 +8078,25 @@
         <v>12</v>
       </c>
       <c r="B12" s="4">
-        <v>205067</v>
+        <v>211553</v>
       </c>
       <c r="C12" s="4">
-        <v>207854</v>
+        <v>214490</v>
       </c>
       <c r="D12" s="4">
-        <v>212900</v>
+        <v>219789</v>
       </c>
       <c r="E12" s="4">
-        <v>257672</v>
+        <v>266814</v>
       </c>
       <c r="F12" s="4">
         <v>9200</v>
       </c>
       <c r="G12" s="4">
-        <v>34385</v>
+        <v>35430</v>
       </c>
       <c r="H12" s="4">
-        <v>316387</v>
+        <v>323825</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8087,25 +8104,25 @@
         <v>13</v>
       </c>
       <c r="B13" s="4">
-        <v>120076</v>
+        <v>123838</v>
       </c>
       <c r="C13" s="4">
-        <v>121291</v>
+        <v>125117</v>
       </c>
       <c r="D13" s="4">
-        <v>123516</v>
+        <v>127454</v>
       </c>
       <c r="E13" s="4">
-        <v>143144</v>
+        <v>148070</v>
       </c>
       <c r="F13" s="4">
         <v>13800</v>
       </c>
       <c r="G13" s="4">
-        <v>20584</v>
+        <v>21210</v>
       </c>
       <c r="H13" s="4">
-        <v>187796</v>
+        <v>191972</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8113,25 +8130,25 @@
         <v>14</v>
       </c>
       <c r="B14" s="4">
-        <v>132114</v>
+        <v>136285</v>
       </c>
       <c r="C14" s="4">
-        <v>133826</v>
+        <v>138088</v>
       </c>
       <c r="D14" s="4">
-        <v>136931</v>
+        <v>141350</v>
       </c>
       <c r="E14" s="4">
-        <v>164410</v>
+        <v>170212</v>
       </c>
       <c r="F14" s="4">
         <v>13800</v>
       </c>
       <c r="G14" s="4">
-        <v>23659</v>
+        <v>24378</v>
       </c>
       <c r="H14" s="4">
-        <v>209747</v>
+        <v>214502</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8139,25 +8156,25 @@
         <v>15</v>
       </c>
       <c r="B15" s="4">
-        <v>145755</v>
+        <v>150385</v>
       </c>
       <c r="C15" s="4">
-        <v>147947</v>
+        <v>152697</v>
       </c>
       <c r="D15" s="4">
-        <v>151942</v>
+        <v>156891</v>
       </c>
       <c r="E15" s="4">
-        <v>187280</v>
+        <v>194007</v>
       </c>
       <c r="F15" s="4">
         <v>13800</v>
       </c>
       <c r="G15" s="4">
-        <v>26735</v>
+        <v>27547</v>
       </c>
       <c r="H15" s="4">
-        <v>233276</v>
+        <v>238660</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8165,25 +8182,25 @@
         <v>16</v>
       </c>
       <c r="B16" s="4">
-        <v>159275</v>
+        <v>164360</v>
       </c>
       <c r="C16" s="4">
-        <v>161965</v>
+        <v>167196</v>
       </c>
       <c r="D16" s="4">
-        <v>166839</v>
+        <v>172315</v>
       </c>
       <c r="E16" s="4">
-        <v>210028</v>
+        <v>217677</v>
       </c>
       <c r="F16" s="4">
         <v>13800</v>
       </c>
       <c r="G16" s="4">
-        <v>29811</v>
+        <v>30718</v>
       </c>
       <c r="H16" s="4">
-        <v>256709</v>
+        <v>262716</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8191,25 +8208,25 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>181818</v>
+        <v>187655</v>
       </c>
       <c r="C17" s="4">
-        <v>185233</v>
+        <v>191254</v>
       </c>
       <c r="D17" s="4">
-        <v>191435</v>
+        <v>197769</v>
       </c>
       <c r="E17" s="4">
-        <v>246411</v>
+        <v>255510</v>
       </c>
       <c r="F17" s="4">
         <v>13800</v>
       </c>
       <c r="G17" s="4">
-        <v>34424</v>
+        <v>35470</v>
       </c>
       <c r="H17" s="4">
-        <v>294093</v>
+        <v>301102</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8217,25 +8234,25 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>204362</v>
+        <v>210949</v>
       </c>
       <c r="C18" s="4">
-        <v>208510</v>
+        <v>215322</v>
       </c>
       <c r="D18" s="4">
-        <v>216050</v>
+        <v>223240</v>
       </c>
       <c r="E18" s="4">
-        <v>282792</v>
+        <v>293341</v>
       </c>
       <c r="F18" s="4">
         <v>13800</v>
       </c>
       <c r="G18" s="4">
-        <v>39038</v>
+        <v>40224</v>
       </c>
       <c r="H18" s="4">
-        <v>331488</v>
+        <v>339497</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8243,25 +8260,25 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>226956</v>
+        <v>234276</v>
       </c>
       <c r="C19" s="4">
-        <v>231594</v>
+        <v>239164</v>
       </c>
       <c r="D19" s="4">
-        <v>240022</v>
+        <v>248015</v>
       </c>
       <c r="E19" s="4">
-        <v>314624</v>
+        <v>326372</v>
       </c>
       <c r="F19" s="4">
         <v>13800</v>
       </c>
       <c r="G19" s="4">
-        <v>42113</v>
+        <v>43394</v>
       </c>
       <c r="H19" s="4">
-        <v>363978</v>
+        <v>372886</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8269,25 +8286,25 @@
         <v>20</v>
       </c>
       <c r="B20" s="4">
-        <v>163016</v>
+        <v>168250</v>
       </c>
       <c r="C20" s="4">
-        <v>166089</v>
+        <v>171488</v>
       </c>
       <c r="D20" s="4">
-        <v>171680</v>
+        <v>177360</v>
       </c>
       <c r="E20" s="4">
-        <v>221155</v>
+        <v>229326</v>
       </c>
       <c r="F20" s="4">
         <v>18400</v>
       </c>
       <c r="G20" s="4">
-        <v>32492</v>
+        <v>33479</v>
       </c>
       <c r="H20" s="4">
-        <v>269680</v>
+        <v>275966</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8295,25 +8312,25 @@
         <v>21</v>
       </c>
       <c r="B21" s="4">
-        <v>177457</v>
+        <v>183192</v>
       </c>
       <c r="C21" s="4">
-        <v>181215</v>
+        <v>187152</v>
       </c>
       <c r="D21" s="4">
-        <v>188045</v>
+        <v>194326</v>
       </c>
       <c r="E21" s="4">
-        <v>248510</v>
+        <v>257833</v>
       </c>
       <c r="F21" s="4">
         <v>18400</v>
       </c>
       <c r="G21" s="4">
-        <v>35962</v>
+        <v>37055</v>
       </c>
       <c r="H21" s="4">
-        <v>295339</v>
+        <v>302360</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8321,25 +8338,25 @@
         <v>22</v>
       </c>
       <c r="B22" s="4">
-        <v>201385</v>
+        <v>207940</v>
       </c>
       <c r="C22" s="4">
-        <v>206169</v>
+        <v>212983</v>
       </c>
       <c r="D22" s="4">
-        <v>214867</v>
+        <v>222118</v>
       </c>
       <c r="E22" s="4">
-        <v>291821</v>
+        <v>302945</v>
       </c>
       <c r="F22" s="4">
         <v>18400</v>
       </c>
       <c r="G22" s="4">
-        <v>41167</v>
+        <v>42418</v>
       </c>
       <c r="H22" s="4">
-        <v>336086</v>
+        <v>344281</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8347,25 +8364,25 @@
         <v>23</v>
       </c>
       <c r="B23" s="4">
-        <v>225314</v>
+        <v>232689</v>
       </c>
       <c r="C23" s="4">
-        <v>231117</v>
+        <v>238806</v>
       </c>
       <c r="D23" s="4">
-        <v>241681</v>
+        <v>249902</v>
       </c>
       <c r="E23" s="4">
-        <v>335124</v>
+        <v>348047</v>
       </c>
       <c r="F23" s="4">
         <v>18400</v>
       </c>
       <c r="G23" s="4">
-        <v>46372</v>
+        <v>47782</v>
       </c>
       <c r="H23" s="4">
-        <v>376830</v>
+        <v>386195</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8373,25 +8390,25 @@
         <v>24</v>
       </c>
       <c r="B24" s="4">
-        <v>249006</v>
+        <v>257164</v>
       </c>
       <c r="C24" s="4">
-        <v>255502</v>
+        <v>264011</v>
       </c>
       <c r="D24" s="4">
-        <v>267296</v>
+        <v>276399</v>
       </c>
       <c r="E24" s="4">
-        <v>371738</v>
+        <v>386095</v>
       </c>
       <c r="F24" s="4">
         <v>18400</v>
       </c>
       <c r="G24" s="4">
-        <v>49842</v>
+        <v>51358</v>
       </c>
       <c r="H24" s="4">
-        <v>411749</v>
+        <v>422132</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8399,25 +8416,25 @@
         <v>25</v>
       </c>
       <c r="B25" s="4">
-        <v>178803</v>
+        <v>184596</v>
       </c>
       <c r="C25" s="4">
-        <v>182764</v>
+        <v>188771</v>
       </c>
       <c r="D25" s="4">
-        <v>189945</v>
+        <v>196313</v>
       </c>
       <c r="E25" s="4">
-        <v>253558</v>
+        <v>263127</v>
       </c>
       <c r="F25" s="4">
         <v>22999</v>
       </c>
       <c r="G25" s="4">
-        <v>38249</v>
+        <v>39411</v>
       </c>
       <c r="H25" s="4">
-        <v>304626</v>
+        <v>311773</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8425,25 +8442,25 @@
         <v>26</v>
       </c>
       <c r="B26" s="4">
-        <v>193181</v>
+        <v>199490</v>
       </c>
       <c r="C26" s="4">
-        <v>198013</v>
+        <v>204584</v>
       </c>
       <c r="D26" s="4">
-        <v>206792</v>
+        <v>213803</v>
       </c>
       <c r="E26" s="4">
-        <v>284533</v>
+        <v>295456</v>
       </c>
       <c r="F26" s="4">
         <v>22999</v>
       </c>
       <c r="G26" s="4">
-        <v>42113</v>
+        <v>43394</v>
       </c>
       <c r="H26" s="4">
-        <v>331523</v>
+        <v>339488</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8451,25 +8468,25 @@
         <v>27</v>
       </c>
       <c r="B27" s="4">
-        <v>218486</v>
+        <v>225684</v>
       </c>
       <c r="C27" s="4">
-        <v>224640</v>
+        <v>232170</v>
       </c>
       <c r="D27" s="4">
-        <v>235814</v>
+        <v>243908</v>
       </c>
       <c r="E27" s="4">
-        <v>334756</v>
+        <v>347828</v>
       </c>
       <c r="F27" s="4">
         <v>22999</v>
       </c>
       <c r="G27" s="4">
-        <v>47910</v>
+        <v>49366</v>
       </c>
       <c r="H27" s="4">
-        <v>375625</v>
+        <v>384928</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8477,25 +8494,25 @@
         <v>28</v>
       </c>
       <c r="B28" s="4">
-        <v>243784</v>
+        <v>251870</v>
       </c>
       <c r="C28" s="4">
-        <v>251257</v>
+        <v>259749</v>
       </c>
       <c r="D28" s="4">
-        <v>261511</v>
+        <v>270518</v>
       </c>
       <c r="E28" s="4">
-        <v>384973</v>
+        <v>400192</v>
       </c>
       <c r="F28" s="4">
         <v>22999</v>
       </c>
       <c r="G28" s="4">
-        <v>53706</v>
+        <v>55339</v>
       </c>
       <c r="H28" s="4">
-        <v>419715</v>
+        <v>430362</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8503,25 +8520,25 @@
         <v>29</v>
       </c>
       <c r="B29" s="4">
-        <v>266546</v>
+        <v>275406</v>
       </c>
       <c r="C29" s="4">
-        <v>274893</v>
+        <v>284203</v>
       </c>
       <c r="D29" s="4">
-        <v>287951</v>
+        <v>297917</v>
       </c>
       <c r="E29" s="4">
-        <v>424342</v>
+        <v>441173</v>
       </c>
       <c r="F29" s="4">
         <v>22999</v>
       </c>
       <c r="G29" s="4">
-        <v>57571</v>
+        <v>59322</v>
       </c>
       <c r="H29" s="4">
-        <v>455001</v>
+        <v>466719</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8529,25 +8546,25 @@
         <v>30</v>
       </c>
       <c r="B30" s="4">
-        <v>284921</v>
+        <v>294418</v>
       </c>
       <c r="C30" s="4">
-        <v>294147</v>
+        <v>304143</v>
       </c>
       <c r="D30" s="4">
-        <v>310913</v>
+        <v>321752</v>
       </c>
       <c r="E30" s="4">
-        <v>459332</v>
+        <v>477639</v>
       </c>
       <c r="F30" s="4">
         <v>22999</v>
       </c>
       <c r="G30" s="4">
-        <v>61435</v>
+        <v>63303</v>
       </c>
       <c r="H30" s="4">
-        <v>485904</v>
+        <v>498561</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8555,25 +8572,25 @@
         <v>31</v>
       </c>
       <c r="B31" s="4">
-        <v>304127</v>
+        <v>314289</v>
       </c>
       <c r="C31" s="4">
-        <v>314235</v>
+        <v>324941</v>
       </c>
       <c r="D31" s="4">
-        <v>332598</v>
+        <v>344228</v>
       </c>
       <c r="E31" s="4">
-        <v>495145</v>
+        <v>514954</v>
       </c>
       <c r="F31" s="4">
         <v>22999</v>
       </c>
       <c r="G31" s="4">
-        <v>65299</v>
+        <v>67285</v>
       </c>
       <c r="H31" s="4">
-        <v>517641</v>
+        <v>531261</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8581,25 +8598,25 @@
         <v>32</v>
       </c>
       <c r="B32" s="4">
-        <v>184614</v>
+        <v>190624</v>
       </c>
       <c r="C32" s="4">
-        <v>189007</v>
+        <v>195254</v>
       </c>
       <c r="D32" s="4">
-        <v>196986</v>
+        <v>203635</v>
       </c>
       <c r="E32" s="4">
-        <v>267664</v>
+        <v>277869</v>
       </c>
       <c r="F32" s="4">
         <v>25299</v>
       </c>
       <c r="G32" s="4">
-        <v>41128</v>
+        <v>42378</v>
       </c>
       <c r="H32" s="4">
-        <v>319998</v>
+        <v>327513</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8607,25 +8624,25 @@
         <v>33</v>
       </c>
       <c r="B33" s="4">
-        <v>201721</v>
+        <v>208340</v>
       </c>
       <c r="C33" s="4">
-        <v>207093</v>
+        <v>214001</v>
       </c>
       <c r="D33" s="4">
-        <v>216849</v>
+        <v>224248</v>
       </c>
       <c r="E33" s="4">
-        <v>303228</v>
+        <v>314973</v>
       </c>
       <c r="F33" s="4">
         <v>25299</v>
       </c>
       <c r="G33" s="4">
-        <v>45189</v>
+        <v>46563</v>
       </c>
       <c r="H33" s="4">
-        <v>350288</v>
+        <v>358744</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8633,25 +8650,25 @@
         <v>34</v>
       </c>
       <c r="B34" s="4">
-        <v>230989</v>
+        <v>238629</v>
       </c>
       <c r="C34" s="4">
-        <v>237827</v>
+        <v>245837</v>
       </c>
       <c r="D34" s="4">
-        <v>250240</v>
+        <v>258875</v>
       </c>
       <c r="E34" s="4">
-        <v>360182</v>
+        <v>374348</v>
       </c>
       <c r="F34" s="4">
         <v>25299</v>
       </c>
       <c r="G34" s="4">
-        <v>51282</v>
+        <v>52840</v>
       </c>
       <c r="H34" s="4">
-        <v>399343</v>
+        <v>409324</v>
       </c>
     </row>
     <row r="35" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8659,25 +8676,25 @@
         <v>35</v>
       </c>
       <c r="B35" s="4">
-        <v>252454</v>
+        <v>260881</v>
       </c>
       <c r="C35" s="4">
-        <v>260752</v>
+        <v>269626</v>
       </c>
       <c r="D35" s="4">
-        <v>275822</v>
+        <v>285454</v>
       </c>
       <c r="E35" s="4">
-        <v>409316</v>
+        <v>425665</v>
       </c>
       <c r="F35" s="4">
         <v>25299</v>
       </c>
       <c r="G35" s="4">
-        <v>57374</v>
+        <v>59118</v>
       </c>
       <c r="H35" s="4">
-        <v>440583</v>
+        <v>451850</v>
       </c>
     </row>
     <row r="36" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8685,25 +8702,25 @@
         <v>36</v>
       </c>
       <c r="B36" s="4">
-        <v>301600</v>
+        <v>311697</v>
       </c>
       <c r="C36" s="4">
-        <v>311854</v>
+        <v>322505</v>
       </c>
       <c r="D36" s="4">
-        <v>330478</v>
+        <v>342066</v>
       </c>
       <c r="E36" s="4">
-        <v>495384</v>
+        <v>515270</v>
       </c>
       <c r="F36" s="4">
         <v>25299</v>
       </c>
       <c r="G36" s="4">
-        <v>65497</v>
+        <v>67487</v>
       </c>
       <c r="H36" s="4">
-        <v>516099</v>
+        <v>529707</v>
       </c>
     </row>
     <row r="37" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8711,25 +8728,25 @@
         <v>37</v>
       </c>
       <c r="B37" s="4">
-        <v>325045</v>
+        <v>335943</v>
       </c>
       <c r="C37" s="4">
-        <v>336276</v>
+        <v>347782</v>
       </c>
       <c r="D37" s="4">
-        <v>356677</v>
+        <v>369209</v>
       </c>
       <c r="E37" s="4">
-        <v>537287</v>
+        <v>558905</v>
       </c>
       <c r="F37" s="4">
         <v>25299</v>
       </c>
       <c r="G37" s="4">
-        <v>69558</v>
+        <v>71673</v>
       </c>
       <c r="H37" s="4">
-        <v>552733</v>
+        <v>567479</v>
       </c>
     </row>
     <row r="38" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8737,25 +8754,25 @@
         <v>38</v>
       </c>
       <c r="B38" s="4">
-        <v>196064</v>
+        <v>202462</v>
       </c>
       <c r="C38" s="4">
-        <v>200897</v>
+        <v>207556</v>
       </c>
       <c r="D38" s="4">
-        <v>209675</v>
+        <v>216775</v>
       </c>
       <c r="E38" s="4">
-        <v>287416</v>
+        <v>298428</v>
       </c>
       <c r="F38" s="4">
         <v>27598</v>
       </c>
       <c r="G38" s="4">
-        <v>44006</v>
+        <v>45344</v>
       </c>
       <c r="H38" s="4">
-        <v>341019</v>
+        <v>349072</v>
       </c>
     </row>
     <row r="39" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8763,25 +8780,25 @@
         <v>39</v>
       </c>
       <c r="B39" s="4">
-        <v>212338</v>
+        <v>219328</v>
       </c>
       <c r="C39" s="4">
-        <v>218248</v>
+        <v>225556</v>
       </c>
       <c r="D39" s="4">
-        <v>224923</v>
+        <v>232567</v>
       </c>
       <c r="E39" s="4">
-        <v>323999</v>
+        <v>336630</v>
       </c>
       <c r="F39" s="4">
         <v>27598</v>
       </c>
       <c r="G39" s="4">
-        <v>48265</v>
+        <v>49732</v>
       </c>
       <c r="H39" s="4">
-        <v>371137</v>
+        <v>380148</v>
       </c>
     </row>
     <row r="40" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8789,25 +8806,25 @@
         <v>40</v>
       </c>
       <c r="B40" s="4">
-        <v>240560</v>
+        <v>248553</v>
       </c>
       <c r="C40" s="4">
-        <v>248075</v>
+        <v>256475</v>
       </c>
       <c r="D40" s="4">
-        <v>261735</v>
+        <v>270823</v>
       </c>
       <c r="E40" s="4">
-        <v>382667</v>
+        <v>397837</v>
       </c>
       <c r="F40" s="4">
         <v>27598</v>
       </c>
       <c r="G40" s="4">
-        <v>54653</v>
+        <v>56314</v>
       </c>
       <c r="H40" s="4">
-        <v>420117</v>
+        <v>430685</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8815,25 +8832,25 @@
         <v>41</v>
       </c>
       <c r="B41" s="4">
-        <v>265738</v>
+        <v>274643</v>
       </c>
       <c r="C41" s="4">
-        <v>274875</v>
+        <v>284274</v>
       </c>
       <c r="D41" s="4">
-        <v>291453</v>
+        <v>301686</v>
       </c>
       <c r="E41" s="4">
-        <v>438297</v>
+        <v>455918</v>
       </c>
       <c r="F41" s="4">
         <v>27598</v>
       </c>
       <c r="G41" s="4">
-        <v>61041</v>
+        <v>62896</v>
       </c>
       <c r="H41" s="4">
-        <v>466078</v>
+        <v>478111</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8841,25 +8858,25 @@
         <v>42</v>
       </c>
       <c r="B42" s="4">
-        <v>291120</v>
+        <v>300893</v>
       </c>
       <c r="C42" s="4">
-        <v>301325</v>
+        <v>311649</v>
       </c>
       <c r="D42" s="4">
-        <v>319858</v>
+        <v>331117</v>
       </c>
       <c r="E42" s="4">
-        <v>483979</v>
+        <v>503494</v>
       </c>
       <c r="F42" s="4">
         <v>27598</v>
       </c>
       <c r="G42" s="4">
-        <v>65299</v>
+        <v>67285</v>
       </c>
       <c r="H42" s="4">
-        <v>505293</v>
+        <v>518560</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8867,25 +8884,25 @@
         <v>43</v>
       </c>
       <c r="B43" s="4">
-        <v>317031</v>
+        <v>327690</v>
       </c>
       <c r="C43" s="4">
-        <v>328311</v>
+        <v>339579</v>
       </c>
       <c r="D43" s="4">
-        <v>348794</v>
+        <v>361092</v>
       </c>
       <c r="E43" s="4">
-        <v>530190</v>
+        <v>551615</v>
       </c>
       <c r="F43" s="4">
         <v>27598</v>
       </c>
       <c r="G43" s="4">
-        <v>69558</v>
+        <v>71673</v>
       </c>
       <c r="H43" s="4">
-        <v>545054</v>
+        <v>559574</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8893,25 +8910,25 @@
         <v>44</v>
       </c>
       <c r="B44" s="4">
-        <v>338872</v>
+        <v>350294</v>
       </c>
       <c r="C44" s="4">
-        <v>351221</v>
+        <v>363309</v>
       </c>
       <c r="D44" s="4">
-        <v>373660</v>
+        <v>386876</v>
       </c>
       <c r="E44" s="4">
-        <v>572332</v>
+        <v>595544</v>
       </c>
       <c r="F44" s="4">
         <v>27598</v>
       </c>
       <c r="G44" s="4">
-        <v>73817</v>
+        <v>76061</v>
       </c>
       <c r="H44" s="4">
-        <v>580731</v>
+        <v>596381</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8919,25 +8936,25 @@
         <v>45</v>
       </c>
       <c r="B45" s="4">
-        <v>215898</v>
+        <v>223019</v>
       </c>
       <c r="C45" s="4">
-        <v>222052</v>
+        <v>229505</v>
       </c>
       <c r="D45" s="4">
-        <v>233226</v>
+        <v>241242</v>
       </c>
       <c r="E45" s="4">
-        <v>332169</v>
+        <v>345162</v>
       </c>
       <c r="F45" s="4">
         <v>34498</v>
       </c>
       <c r="G45" s="4">
-        <v>52642</v>
+        <v>54243</v>
       </c>
       <c r="H45" s="4">
-        <v>389568</v>
+        <v>398793</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8945,25 +8962,25 @@
         <v>46</v>
       </c>
       <c r="B46" s="4">
-        <v>233576</v>
+        <v>241356</v>
       </c>
       <c r="C46" s="4">
-        <v>241091</v>
+        <v>249277</v>
       </c>
       <c r="D46" s="4">
-        <v>254751</v>
+        <v>263626</v>
       </c>
       <c r="E46" s="4">
-        <v>375682</v>
+        <v>390640</v>
       </c>
       <c r="F46" s="4">
         <v>34498</v>
       </c>
       <c r="G46" s="4">
-        <v>57492</v>
+        <v>59239</v>
       </c>
       <c r="H46" s="4">
-        <v>423052</v>
+        <v>433407</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8971,25 +8988,25 @@
         <v>47</v>
       </c>
       <c r="B47" s="4">
-        <v>265374</v>
+        <v>274306</v>
       </c>
       <c r="C47" s="4">
-        <v>274951</v>
+        <v>284401</v>
       </c>
       <c r="D47" s="4">
-        <v>292328</v>
+        <v>302652</v>
       </c>
       <c r="E47" s="4">
-        <v>446245</v>
+        <v>464313</v>
       </c>
       <c r="F47" s="4">
         <v>34498</v>
       </c>
       <c r="G47" s="4">
-        <v>64768</v>
+        <v>66736</v>
       </c>
       <c r="H47" s="4">
-        <v>478590</v>
+        <v>490800</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8997,25 +9014,25 @@
         <v>48</v>
       </c>
       <c r="B48" s="4">
-        <v>291124</v>
+        <v>301026</v>
       </c>
       <c r="C48" s="4">
-        <v>302738</v>
+        <v>313269</v>
       </c>
       <c r="D48" s="4">
-        <v>323848</v>
+        <v>335441</v>
       </c>
       <c r="E48" s="4">
-        <v>510742</v>
+        <v>531739</v>
       </c>
       <c r="F48" s="4">
         <v>34498</v>
       </c>
       <c r="G48" s="4">
-        <v>72042</v>
+        <v>74233</v>
       </c>
       <c r="H48" s="4">
-        <v>528042</v>
+        <v>541924</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9023,25 +9040,25 @@
         <v>49</v>
       </c>
       <c r="B49" s="4">
-        <v>317892</v>
+        <v>328732</v>
       </c>
       <c r="C49" s="4">
-        <v>322725</v>
+        <v>333857</v>
       </c>
       <c r="D49" s="4">
-        <v>354471</v>
+        <v>367201</v>
       </c>
       <c r="E49" s="4">
-        <v>563365</v>
+        <v>586604</v>
       </c>
       <c r="F49" s="4">
         <v>34498</v>
       </c>
       <c r="G49" s="4">
-        <v>76892</v>
+        <v>79230</v>
       </c>
       <c r="H49" s="4">
-        <v>554331</v>
+        <v>568799</v>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9049,25 +9066,25 @@
         <v>50</v>
       </c>
       <c r="B50" s="4">
-        <v>347270</v>
+        <v>359126</v>
       </c>
       <c r="C50" s="4">
-        <v>361633</v>
+        <v>374264</v>
       </c>
       <c r="D50" s="4">
-        <v>387706</v>
+        <v>401650</v>
       </c>
       <c r="E50" s="4">
-        <v>618569</v>
+        <v>644128</v>
       </c>
       <c r="F50" s="4">
         <v>34498</v>
       </c>
       <c r="G50" s="4">
-        <v>81743</v>
+        <v>84227</v>
       </c>
       <c r="H50" s="4">
-        <v>615843</v>
+        <v>632613</v>
       </c>
     </row>
     <row r="51" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9075,25 +9092,25 @@
         <v>51</v>
       </c>
       <c r="B51" s="4">
-        <v>367999</v>
+        <v>380610</v>
       </c>
       <c r="C51" s="4">
-        <v>383715</v>
+        <v>397174</v>
       </c>
       <c r="D51" s="4">
-        <v>412274</v>
+        <v>427169</v>
       </c>
       <c r="E51" s="4">
-        <v>665135</v>
+        <v>692753</v>
       </c>
       <c r="F51" s="4">
         <v>34498</v>
       </c>
       <c r="G51" s="4">
-        <v>86593</v>
+        <v>89225</v>
       </c>
       <c r="H51" s="4">
-        <v>652371</v>
+        <v>670363</v>
       </c>
     </row>
     <row r="52" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9101,25 +9118,25 @@
         <v>52</v>
       </c>
       <c r="B52" s="4">
-        <v>287171</v>
+        <v>296657</v>
       </c>
       <c r="C52" s="4">
-        <v>295518</v>
+        <v>305455</v>
       </c>
       <c r="D52" s="4">
-        <v>310686</v>
+        <v>321386</v>
       </c>
       <c r="E52" s="4">
-        <v>444958</v>
+        <v>462414</v>
       </c>
       <c r="F52" s="4">
         <v>45998</v>
       </c>
       <c r="G52" s="4">
-        <v>67034</v>
+        <v>69072</v>
       </c>
       <c r="H52" s="4">
-        <v>508688</v>
+        <v>521033</v>
       </c>
     </row>
     <row r="53" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9127,25 +9144,25 @@
         <v>53</v>
       </c>
       <c r="B53" s="4">
-        <v>315358</v>
+        <v>325867</v>
       </c>
       <c r="C53" s="4">
-        <v>325562</v>
+        <v>336623</v>
       </c>
       <c r="D53" s="4">
-        <v>344096</v>
+        <v>356091</v>
       </c>
       <c r="E53" s="4">
-        <v>508216</v>
+        <v>528469</v>
       </c>
       <c r="F53" s="4">
         <v>45998</v>
       </c>
       <c r="G53" s="4">
-        <v>72870</v>
+        <v>75085</v>
       </c>
       <c r="H53" s="4">
-        <v>555981</v>
+        <v>569984</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9153,25 +9170,25 @@
         <v>54</v>
       </c>
       <c r="B54" s="4">
-        <v>354184</v>
+        <v>366187</v>
       </c>
       <c r="C54" s="4">
-        <v>363932</v>
+        <v>376477</v>
       </c>
       <c r="D54" s="4">
-        <v>387527</v>
+        <v>401260</v>
       </c>
       <c r="E54" s="4">
-        <v>596412</v>
+        <v>620654</v>
       </c>
       <c r="F54" s="4">
         <v>45998</v>
       </c>
       <c r="G54" s="4">
-        <v>81624</v>
+        <v>84105</v>
       </c>
       <c r="H54" s="4">
-        <v>620219</v>
+        <v>636510</v>
       </c>
     </row>
     <row r="55" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9179,25 +9196,25 @@
         <v>55</v>
       </c>
       <c r="B55" s="4">
-        <v>387383</v>
+        <v>400662</v>
       </c>
       <c r="C55" s="4">
-        <v>399225</v>
+        <v>413163</v>
       </c>
       <c r="D55" s="4">
-        <v>427866</v>
+        <v>443245</v>
       </c>
       <c r="E55" s="4">
-        <v>681514</v>
+        <v>709654</v>
       </c>
       <c r="F55" s="4">
         <v>45998</v>
       </c>
       <c r="G55" s="4">
-        <v>90378</v>
+        <v>93126</v>
       </c>
       <c r="H55" s="4">
-        <v>681390</v>
+        <v>699877</v>
       </c>
     </row>
     <row r="56" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9205,25 +9222,25 @@
         <v>56</v>
       </c>
       <c r="B56" s="4">
-        <v>423370</v>
+        <v>437920</v>
       </c>
       <c r="C56" s="4">
-        <v>436607</v>
+        <v>451892</v>
       </c>
       <c r="D56" s="4">
-        <v>468622</v>
+        <v>485518</v>
       </c>
       <c r="E56" s="4">
-        <v>752100</v>
+        <v>783258</v>
       </c>
       <c r="F56" s="4">
         <v>45998</v>
       </c>
       <c r="G56" s="4">
-        <v>96214</v>
+        <v>99138</v>
       </c>
       <c r="H56" s="4">
-        <v>736020</v>
+        <v>756389</v>
       </c>
     </row>
     <row r="57" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9231,25 +9248,25 @@
         <v>57</v>
       </c>
       <c r="B57" s="4">
-        <v>449498</v>
+        <v>465017</v>
       </c>
       <c r="C57" s="4">
-        <v>464128</v>
+        <v>480460</v>
       </c>
       <c r="D57" s="4">
-        <v>499508</v>
+        <v>517622</v>
       </c>
       <c r="E57" s="4">
-        <v>812824</v>
+        <v>846702</v>
       </c>
       <c r="F57" s="4">
         <v>45998</v>
       </c>
       <c r="G57" s="4">
-        <v>102050</v>
+        <v>105153</v>
       </c>
       <c r="H57" s="4">
-        <v>780791</v>
+        <v>802741</v>
       </c>
     </row>
     <row r="58" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9257,25 +9274,25 @@
         <v>58</v>
       </c>
       <c r="B58" s="4">
-        <v>480790</v>
+        <v>497440</v>
       </c>
       <c r="C58" s="4">
-        <v>496815</v>
+        <v>514354</v>
       </c>
       <c r="D58" s="4">
-        <v>535562</v>
+        <v>555050</v>
       </c>
       <c r="E58" s="4">
-        <v>878726</v>
+        <v>915481</v>
       </c>
       <c r="F58" s="4">
         <v>45998</v>
       </c>
       <c r="G58" s="4">
-        <v>107886</v>
+        <v>111165</v>
       </c>
       <c r="H58" s="4">
-        <v>830726</v>
+        <v>854419</v>
       </c>
     </row>
     <row r="59" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9283,25 +9300,25 @@
         <v>59</v>
       </c>
       <c r="B59" s="4">
-        <v>504830</v>
+        <v>522312</v>
       </c>
       <c r="C59" s="4">
-        <v>521655</v>
+        <v>540071</v>
       </c>
       <c r="D59" s="4">
-        <v>562340</v>
+        <v>582803</v>
       </c>
       <c r="E59" s="4">
-        <v>922663</v>
+        <v>961255</v>
       </c>
       <c r="F59" s="4">
         <v>48298</v>
       </c>
       <c r="G59" s="4">
-        <v>113280</v>
+        <v>116723</v>
       </c>
       <c r="H59" s="4">
-        <v>872263</v>
+        <v>897140</v>
       </c>
     </row>
   </sheetData>
@@ -9375,25 +9392,25 @@
         <v>99</v>
       </c>
       <c r="B6" s="4">
-        <v>120467</v>
+        <v>124599</v>
       </c>
       <c r="C6" s="4">
-        <v>121172</v>
+        <v>125338</v>
       </c>
       <c r="D6" s="4">
-        <v>122450</v>
+        <v>126683</v>
       </c>
       <c r="E6" s="4">
-        <v>128635</v>
+        <v>133183</v>
       </c>
       <c r="F6" s="4">
-        <v>121576</v>
+        <v>125764</v>
       </c>
       <c r="G6" s="4">
-        <v>134330</v>
+        <v>139169</v>
       </c>
       <c r="H6" s="4">
-        <v>156994</v>
+        <v>161365</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9401,25 +9418,25 @@
         <v>100</v>
       </c>
       <c r="B7" s="4">
-        <v>128119</v>
+        <v>132530</v>
       </c>
       <c r="C7" s="4">
-        <v>129059</v>
+        <v>133517</v>
       </c>
       <c r="D7" s="4">
-        <v>130768</v>
+        <v>135314</v>
       </c>
       <c r="E7" s="4">
-        <v>139014</v>
+        <v>143981</v>
       </c>
       <c r="F7" s="4">
-        <v>129607</v>
+        <v>134094</v>
       </c>
       <c r="G7" s="4">
-        <v>146618</v>
+        <v>151975</v>
       </c>
       <c r="H7" s="4">
-        <v>170197</v>
+        <v>174930</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9427,25 +9444,25 @@
         <v>101</v>
       </c>
       <c r="B8" s="4">
-        <v>135818</v>
+        <v>140507</v>
       </c>
       <c r="C8" s="4">
-        <v>136991</v>
+        <v>141741</v>
       </c>
       <c r="D8" s="4">
-        <v>139130</v>
+        <v>143989</v>
       </c>
       <c r="E8" s="4">
-        <v>149437</v>
+        <v>154822</v>
       </c>
       <c r="F8" s="4">
-        <v>137682</v>
+        <v>142468</v>
       </c>
       <c r="G8" s="4">
-        <v>158953</v>
+        <v>164824</v>
       </c>
       <c r="H8" s="4">
-        <v>183449</v>
+        <v>188541</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9453,25 +9470,25 @@
         <v>102</v>
       </c>
       <c r="B9" s="4">
-        <v>143489</v>
+        <v>148456</v>
       </c>
       <c r="C9" s="4">
-        <v>144897</v>
+        <v>149938</v>
       </c>
       <c r="D9" s="4">
-        <v>147468</v>
+        <v>152639</v>
       </c>
       <c r="E9" s="4">
-        <v>159835</v>
+        <v>165638</v>
       </c>
       <c r="F9" s="4">
-        <v>145733</v>
+        <v>150814</v>
       </c>
       <c r="G9" s="4">
-        <v>171261</v>
+        <v>177647</v>
       </c>
       <c r="H9" s="4">
-        <v>196672</v>
+        <v>202124</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9479,25 +9496,25 @@
         <v>103</v>
       </c>
       <c r="B10" s="4">
-        <v>151177</v>
+        <v>156425</v>
       </c>
       <c r="C10" s="4">
-        <v>152821</v>
+        <v>158152</v>
       </c>
       <c r="D10" s="4">
-        <v>155821</v>
+        <v>161306</v>
       </c>
       <c r="E10" s="4">
-        <v>170250</v>
+        <v>176472</v>
       </c>
       <c r="F10" s="4">
-        <v>153799</v>
+        <v>159180</v>
       </c>
       <c r="G10" s="4">
-        <v>183586</v>
+        <v>190488</v>
       </c>
       <c r="H10" s="4">
-        <v>209914</v>
+        <v>215725</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9505,25 +9522,25 @@
         <v>104</v>
       </c>
       <c r="B11" s="4">
-        <v>158856</v>
+        <v>164382</v>
       </c>
       <c r="C11" s="4">
-        <v>160735</v>
+        <v>166357</v>
       </c>
       <c r="D11" s="4">
-        <v>164167</v>
+        <v>169963</v>
       </c>
       <c r="E11" s="4">
-        <v>180656</v>
+        <v>187296</v>
       </c>
       <c r="F11" s="4">
-        <v>161857</v>
+        <v>167536</v>
       </c>
       <c r="G11" s="4">
-        <v>195903</v>
+        <v>203320</v>
       </c>
       <c r="H11" s="4">
-        <v>223143</v>
+        <v>229315</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9531,25 +9548,25 @@
         <v>105</v>
       </c>
       <c r="B12" s="4">
-        <v>166510</v>
+        <v>172315</v>
       </c>
       <c r="C12" s="4">
-        <v>168624</v>
+        <v>174535</v>
       </c>
       <c r="D12" s="4">
-        <v>172485</v>
+        <v>178594</v>
       </c>
       <c r="E12" s="4">
-        <v>191037</v>
+        <v>198094</v>
       </c>
       <c r="F12" s="4">
-        <v>169889</v>
+        <v>175866</v>
       </c>
       <c r="G12" s="4">
-        <v>208193</v>
+        <v>216125</v>
       </c>
       <c r="H12" s="4">
-        <v>236351</v>
+        <v>242880</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9557,25 +9574,25 @@
         <v>106</v>
       </c>
       <c r="B13" s="4">
-        <v>128137</v>
+        <v>132548</v>
       </c>
       <c r="C13" s="4">
-        <v>129077</v>
+        <v>133535</v>
       </c>
       <c r="D13" s="4">
-        <v>130786</v>
+        <v>135332</v>
       </c>
       <c r="E13" s="4">
-        <v>139032</v>
+        <v>143999</v>
       </c>
       <c r="F13" s="4">
-        <v>129625</v>
+        <v>134112</v>
       </c>
       <c r="G13" s="4">
-        <v>146636</v>
+        <v>151993</v>
       </c>
       <c r="H13" s="4">
-        <v>170215</v>
+        <v>174948</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9583,25 +9600,25 @@
         <v>107</v>
       </c>
       <c r="B14" s="4">
-        <v>136196</v>
+        <v>140904</v>
       </c>
       <c r="C14" s="4">
-        <v>137435</v>
+        <v>142206</v>
       </c>
       <c r="D14" s="4">
-        <v>139731</v>
+        <v>144621</v>
       </c>
       <c r="E14" s="4">
-        <v>150703</v>
+        <v>156152</v>
       </c>
       <c r="F14" s="4">
-        <v>138165</v>
+        <v>142975</v>
       </c>
       <c r="G14" s="4">
-        <v>160847</v>
+        <v>166815</v>
       </c>
       <c r="H14" s="4">
-        <v>184335</v>
+        <v>189472</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9609,25 +9626,25 @@
         <v>108</v>
       </c>
       <c r="B15" s="4">
-        <v>144232</v>
+        <v>149238</v>
       </c>
       <c r="C15" s="4">
-        <v>145784</v>
+        <v>150869</v>
       </c>
       <c r="D15" s="4">
-        <v>148668</v>
+        <v>153900</v>
       </c>
       <c r="E15" s="4">
-        <v>162366</v>
+        <v>168298</v>
       </c>
       <c r="F15" s="4">
-        <v>146698</v>
+        <v>151829</v>
       </c>
       <c r="G15" s="4">
-        <v>175049</v>
+        <v>181629</v>
       </c>
       <c r="H15" s="4">
-        <v>198445</v>
+        <v>203988</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9635,25 +9652,25 @@
         <v>109</v>
       </c>
       <c r="B16" s="4">
-        <v>152267</v>
+        <v>157572</v>
       </c>
       <c r="C16" s="4">
-        <v>154133</v>
+        <v>159533</v>
       </c>
       <c r="D16" s="4">
-        <v>157604</v>
+        <v>163180</v>
       </c>
       <c r="E16" s="4">
-        <v>174029</v>
+        <v>180445</v>
       </c>
       <c r="F16" s="4">
-        <v>155229</v>
+        <v>160685</v>
       </c>
       <c r="G16" s="4">
-        <v>189251</v>
+        <v>196443</v>
       </c>
       <c r="H16" s="4">
-        <v>212556</v>
+        <v>218504</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9661,25 +9678,25 @@
         <v>110</v>
       </c>
       <c r="B17" s="4">
-        <v>160344</v>
+        <v>165945</v>
       </c>
       <c r="C17" s="4">
-        <v>162510</v>
+        <v>168221</v>
       </c>
       <c r="D17" s="4">
-        <v>166567</v>
+        <v>172486</v>
       </c>
       <c r="E17" s="4">
-        <v>185718</v>
+        <v>192615</v>
       </c>
       <c r="F17" s="4">
-        <v>163787</v>
+        <v>169566</v>
       </c>
       <c r="G17" s="4">
-        <v>203479</v>
+        <v>211284</v>
       </c>
       <c r="H17" s="4">
-        <v>226693</v>
+        <v>233044</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9687,25 +9704,25 @@
         <v>111</v>
       </c>
       <c r="B18" s="4">
-        <v>168379</v>
+        <v>174279</v>
       </c>
       <c r="C18" s="4">
-        <v>170857</v>
+        <v>176885</v>
       </c>
       <c r="D18" s="4">
-        <v>175503</v>
+        <v>181766</v>
       </c>
       <c r="E18" s="4">
-        <v>197380</v>
+        <v>204762</v>
       </c>
       <c r="F18" s="4">
-        <v>172320</v>
+        <v>178420</v>
       </c>
       <c r="G18" s="4">
-        <v>217680</v>
+        <v>226098</v>
       </c>
       <c r="H18" s="4">
-        <v>240801</v>
+        <v>247560</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9713,25 +9730,25 @@
         <v>112</v>
       </c>
       <c r="B19" s="4">
-        <v>176417</v>
+        <v>182613</v>
       </c>
       <c r="C19" s="4">
-        <v>179208</v>
+        <v>185548</v>
       </c>
       <c r="D19" s="4">
-        <v>184439</v>
+        <v>191047</v>
       </c>
       <c r="E19" s="4">
-        <v>209045</v>
+        <v>216908</v>
       </c>
       <c r="F19" s="4">
-        <v>180852</v>
+        <v>187275</v>
       </c>
       <c r="G19" s="4">
-        <v>231883</v>
+        <v>240913</v>
       </c>
       <c r="H19" s="4">
-        <v>254914</v>
+        <v>262076</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9739,25 +9756,25 @@
         <v>113</v>
       </c>
       <c r="B20" s="4">
-        <v>135818</v>
+        <v>140507</v>
       </c>
       <c r="C20" s="4">
-        <v>136991</v>
+        <v>141741</v>
       </c>
       <c r="D20" s="4">
-        <v>139130</v>
+        <v>143989</v>
       </c>
       <c r="E20" s="4">
-        <v>149437</v>
+        <v>154822</v>
       </c>
       <c r="F20" s="4">
-        <v>137682</v>
+        <v>142468</v>
       </c>
       <c r="G20" s="4">
-        <v>158953</v>
+        <v>164824</v>
       </c>
       <c r="H20" s="4">
-        <v>183449</v>
+        <v>188541</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9765,25 +9782,25 @@
         <v>114</v>
       </c>
       <c r="B21" s="4">
-        <v>144232</v>
+        <v>149238</v>
       </c>
       <c r="C21" s="4">
-        <v>145784</v>
+        <v>150869</v>
       </c>
       <c r="D21" s="4">
-        <v>148668</v>
+        <v>153900</v>
       </c>
       <c r="E21" s="4">
-        <v>162366</v>
+        <v>168298</v>
       </c>
       <c r="F21" s="4">
-        <v>146698</v>
+        <v>151829</v>
       </c>
       <c r="G21" s="4">
-        <v>175049</v>
+        <v>181629</v>
       </c>
       <c r="H21" s="4">
-        <v>198445</v>
+        <v>203988</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9791,25 +9808,25 @@
         <v>115</v>
       </c>
       <c r="B22" s="4">
-        <v>152633</v>
+        <v>157956</v>
       </c>
       <c r="C22" s="4">
-        <v>154577</v>
+        <v>159999</v>
       </c>
       <c r="D22" s="4">
-        <v>158204</v>
+        <v>163812</v>
       </c>
       <c r="E22" s="4">
-        <v>175294</v>
+        <v>181775</v>
       </c>
       <c r="F22" s="4">
-        <v>155712</v>
+        <v>161192</v>
       </c>
       <c r="G22" s="4">
-        <v>191146</v>
+        <v>198435</v>
       </c>
       <c r="H22" s="4">
-        <v>213443</v>
+        <v>219437</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9817,25 +9834,25 @@
         <v>116</v>
       </c>
       <c r="B23" s="4">
-        <v>161074</v>
+        <v>166713</v>
       </c>
       <c r="C23" s="4">
-        <v>163396</v>
+        <v>169154</v>
       </c>
       <c r="D23" s="4">
-        <v>167766</v>
+        <v>173747</v>
       </c>
       <c r="E23" s="4">
-        <v>188380</v>
+        <v>195413</v>
       </c>
       <c r="F23" s="4">
-        <v>164754</v>
+        <v>170579</v>
       </c>
       <c r="G23" s="4">
-        <v>207267</v>
+        <v>215267</v>
       </c>
       <c r="H23" s="4">
-        <v>228467</v>
+        <v>234910</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9843,25 +9860,25 @@
         <v>117</v>
       </c>
       <c r="B24" s="4">
-        <v>169489</v>
+        <v>175444</v>
       </c>
       <c r="C24" s="4">
-        <v>172189</v>
+        <v>178283</v>
       </c>
       <c r="D24" s="4">
-        <v>177302</v>
+        <v>183659</v>
       </c>
       <c r="E24" s="4">
-        <v>201438</v>
+        <v>209027</v>
       </c>
       <c r="F24" s="4">
-        <v>173768</v>
+        <v>179942</v>
       </c>
       <c r="G24" s="4">
-        <v>223363</v>
+        <v>232072</v>
       </c>
       <c r="H24" s="4">
-        <v>243464</v>
+        <v>250357</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9869,25 +9886,25 @@
         <v>118</v>
       </c>
       <c r="B25" s="4">
-        <v>177903</v>
+        <v>184177</v>
       </c>
       <c r="C25" s="4">
-        <v>180983</v>
+        <v>187412</v>
       </c>
       <c r="D25" s="4">
-        <v>186840</v>
+        <v>193569</v>
       </c>
       <c r="E25" s="4">
-        <v>214498</v>
+        <v>222639</v>
       </c>
       <c r="F25" s="4">
-        <v>182782</v>
+        <v>189305</v>
       </c>
       <c r="G25" s="4">
-        <v>239460</v>
+        <v>248878</v>
       </c>
       <c r="H25" s="4">
-        <v>258464</v>
+        <v>265805</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9895,25 +9912,25 @@
         <v>119</v>
       </c>
       <c r="B26" s="4">
-        <v>186327</v>
+        <v>192915</v>
       </c>
       <c r="C26" s="4">
-        <v>189783</v>
+        <v>196550</v>
       </c>
       <c r="D26" s="4">
-        <v>196384</v>
+        <v>203488</v>
       </c>
       <c r="E26" s="4">
-        <v>227566</v>
+        <v>236261</v>
       </c>
       <c r="F26" s="4">
-        <v>191806</v>
+        <v>198675</v>
       </c>
       <c r="G26" s="4">
-        <v>255565</v>
+        <v>265690</v>
       </c>
       <c r="H26" s="4">
-        <v>273468</v>
+        <v>281262</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9921,25 +9938,25 @@
         <v>120</v>
       </c>
       <c r="B27" s="4">
-        <v>143489</v>
+        <v>148456</v>
       </c>
       <c r="C27" s="4">
-        <v>144897</v>
+        <v>149938</v>
       </c>
       <c r="D27" s="4">
-        <v>147468</v>
+        <v>152639</v>
       </c>
       <c r="E27" s="4">
-        <v>159835</v>
+        <v>165638</v>
       </c>
       <c r="F27" s="4">
-        <v>145733</v>
+        <v>150814</v>
       </c>
       <c r="G27" s="4">
-        <v>171261</v>
+        <v>177647</v>
       </c>
       <c r="H27" s="4">
-        <v>196672</v>
+        <v>202124</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9947,25 +9964,25 @@
         <v>121</v>
       </c>
       <c r="B28" s="4">
-        <v>152267</v>
+        <v>157572</v>
       </c>
       <c r="C28" s="4">
-        <v>154133</v>
+        <v>159533</v>
       </c>
       <c r="D28" s="4">
-        <v>157604</v>
+        <v>163180</v>
       </c>
       <c r="E28" s="4">
-        <v>174029</v>
+        <v>180445</v>
       </c>
       <c r="F28" s="4">
-        <v>155229</v>
+        <v>160685</v>
       </c>
       <c r="G28" s="4">
-        <v>189251</v>
+        <v>196443</v>
       </c>
       <c r="H28" s="4">
-        <v>212556</v>
+        <v>218504</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9973,25 +9990,25 @@
         <v>122</v>
       </c>
       <c r="B29" s="4">
-        <v>161074</v>
+        <v>166713</v>
       </c>
       <c r="C29" s="4">
-        <v>163396</v>
+        <v>169154</v>
       </c>
       <c r="D29" s="4">
-        <v>167766</v>
+        <v>173747</v>
       </c>
       <c r="E29" s="4">
-        <v>188380</v>
+        <v>195413</v>
       </c>
       <c r="F29" s="4">
-        <v>164754</v>
+        <v>170579</v>
       </c>
       <c r="G29" s="4">
-        <v>207267</v>
+        <v>215267</v>
       </c>
       <c r="H29" s="4">
-        <v>228467</v>
+        <v>234910</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9999,25 +10016,25 @@
         <v>123</v>
       </c>
       <c r="B30" s="4">
-        <v>169867</v>
+        <v>175843</v>
       </c>
       <c r="C30" s="4">
-        <v>172632</v>
+        <v>178749</v>
       </c>
       <c r="D30" s="4">
-        <v>177903</v>
+        <v>184289</v>
       </c>
       <c r="E30" s="4">
-        <v>202704</v>
+        <v>210357</v>
       </c>
       <c r="F30" s="4">
-        <v>174250</v>
+        <v>180450</v>
       </c>
       <c r="G30" s="4">
-        <v>225258</v>
+        <v>234063</v>
       </c>
       <c r="H30" s="4">
-        <v>244351</v>
+        <v>251289</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10025,25 +10042,25 @@
         <v>124</v>
       </c>
       <c r="B31" s="4">
-        <v>178647</v>
+        <v>184958</v>
       </c>
       <c r="C31" s="4">
-        <v>181870</v>
+        <v>188345</v>
       </c>
       <c r="D31" s="4">
-        <v>188040</v>
+        <v>194831</v>
       </c>
       <c r="E31" s="4">
-        <v>217029</v>
+        <v>225300</v>
       </c>
       <c r="F31" s="4">
-        <v>183748</v>
+        <v>190319</v>
       </c>
       <c r="G31" s="4">
-        <v>243249</v>
+        <v>252859</v>
       </c>
       <c r="H31" s="4">
-        <v>260237</v>
+        <v>267671</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10051,25 +10068,25 @@
         <v>125</v>
       </c>
       <c r="B32" s="4">
-        <v>187435</v>
+        <v>194082</v>
       </c>
       <c r="C32" s="4">
-        <v>191115</v>
+        <v>197948</v>
       </c>
       <c r="D32" s="4">
-        <v>198185</v>
+        <v>205381</v>
       </c>
       <c r="E32" s="4">
-        <v>231362</v>
+        <v>240252</v>
       </c>
       <c r="F32" s="4">
-        <v>193254</v>
+        <v>200197</v>
       </c>
       <c r="G32" s="4">
-        <v>261247</v>
+        <v>271663</v>
       </c>
       <c r="H32" s="4">
-        <v>276131</v>
+        <v>284058</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10077,25 +10094,25 @@
         <v>126</v>
       </c>
       <c r="B33" s="4">
-        <v>196233</v>
+        <v>203215</v>
       </c>
       <c r="C33" s="4">
-        <v>200369</v>
+        <v>207562</v>
       </c>
       <c r="D33" s="4">
-        <v>208340</v>
+        <v>215939</v>
       </c>
       <c r="E33" s="4">
-        <v>245703</v>
+        <v>255212</v>
       </c>
       <c r="F33" s="4">
-        <v>202769</v>
+        <v>210084</v>
       </c>
       <c r="G33" s="4">
-        <v>279255</v>
+        <v>290478</v>
       </c>
       <c r="H33" s="4">
-        <v>292033</v>
+        <v>300458</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10103,25 +10120,25 @@
         <v>127</v>
       </c>
       <c r="B34" s="4">
-        <v>151159</v>
+        <v>156407</v>
       </c>
       <c r="C34" s="4">
-        <v>152803</v>
+        <v>158134</v>
       </c>
       <c r="D34" s="4">
-        <v>155803</v>
+        <v>161288</v>
       </c>
       <c r="E34" s="4">
-        <v>170232</v>
+        <v>176454</v>
       </c>
       <c r="F34" s="4">
-        <v>153781</v>
+        <v>159162</v>
       </c>
       <c r="G34" s="4">
-        <v>183568</v>
+        <v>190470</v>
       </c>
       <c r="H34" s="4">
-        <v>209896</v>
+        <v>215708</v>
       </c>
     </row>
     <row r="35" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10129,25 +10146,25 @@
         <v>202</v>
       </c>
       <c r="B35" s="4">
-        <v>169489</v>
+        <v>175444</v>
       </c>
       <c r="C35" s="4">
-        <v>172189</v>
+        <v>178283</v>
       </c>
       <c r="D35" s="4">
-        <v>177302</v>
+        <v>183659</v>
       </c>
       <c r="E35" s="4">
-        <v>201438</v>
+        <v>209027</v>
       </c>
       <c r="F35" s="4">
-        <v>173768</v>
+        <v>179942</v>
       </c>
       <c r="G35" s="4">
-        <v>223363</v>
+        <v>232072</v>
       </c>
       <c r="H35" s="4">
-        <v>243464</v>
+        <v>250357</v>
       </c>
     </row>
     <row r="36" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10155,25 +10172,25 @@
         <v>129</v>
       </c>
       <c r="B36" s="4">
-        <v>178647</v>
+        <v>184958</v>
       </c>
       <c r="C36" s="4">
-        <v>181870</v>
+        <v>188345</v>
       </c>
       <c r="D36" s="4">
-        <v>188040</v>
+        <v>194831</v>
       </c>
       <c r="E36" s="4">
-        <v>217029</v>
+        <v>225300</v>
       </c>
       <c r="F36" s="4">
-        <v>183748</v>
+        <v>190319</v>
       </c>
       <c r="G36" s="4">
-        <v>243249</v>
+        <v>252859</v>
       </c>
       <c r="H36" s="4">
-        <v>260237</v>
+        <v>267671</v>
       </c>
     </row>
     <row r="37" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10181,25 +10198,25 @@
         <v>130</v>
       </c>
       <c r="B37" s="4">
-        <v>187801</v>
+        <v>194465</v>
       </c>
       <c r="C37" s="4">
-        <v>191558</v>
+        <v>198414</v>
       </c>
       <c r="D37" s="4">
-        <v>198786</v>
+        <v>206011</v>
       </c>
       <c r="E37" s="4">
-        <v>232628</v>
+        <v>241582</v>
       </c>
       <c r="F37" s="4">
-        <v>193737</v>
+        <v>200705</v>
       </c>
       <c r="G37" s="4">
-        <v>263142</v>
+        <v>273655</v>
       </c>
       <c r="H37" s="4">
-        <v>277018</v>
+        <v>284991</v>
       </c>
     </row>
     <row r="38" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10207,25 +10224,25 @@
         <v>131</v>
       </c>
       <c r="B38" s="4">
-        <v>196964</v>
+        <v>203983</v>
       </c>
       <c r="C38" s="4">
-        <v>201256</v>
+        <v>208494</v>
       </c>
       <c r="D38" s="4">
-        <v>209539</v>
+        <v>217202</v>
       </c>
       <c r="E38" s="4">
-        <v>248234</v>
+        <v>257873</v>
       </c>
       <c r="F38" s="4">
-        <v>203734</v>
+        <v>211099</v>
       </c>
       <c r="G38" s="4">
-        <v>283043</v>
+        <v>294461</v>
       </c>
       <c r="H38" s="4">
-        <v>293807</v>
+        <v>302322</v>
       </c>
     </row>
     <row r="39" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10233,25 +10250,25 @@
         <v>132</v>
       </c>
       <c r="B39" s="4">
-        <v>206108</v>
+        <v>213481</v>
       </c>
       <c r="C39" s="4">
-        <v>210935</v>
+        <v>218555</v>
       </c>
       <c r="D39" s="4">
-        <v>220276</v>
+        <v>228373</v>
       </c>
       <c r="E39" s="4">
-        <v>263824</v>
+        <v>274144</v>
       </c>
       <c r="F39" s="4">
-        <v>213713</v>
+        <v>221476</v>
       </c>
       <c r="G39" s="4">
-        <v>302928</v>
+        <v>315246</v>
       </c>
       <c r="H39" s="4">
-        <v>310577</v>
+        <v>319634</v>
       </c>
     </row>
     <row r="40" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10259,25 +10276,25 @@
         <v>133</v>
       </c>
       <c r="B40" s="4">
-        <v>158856</v>
+        <v>164382</v>
       </c>
       <c r="C40" s="4">
-        <v>160735</v>
+        <v>166357</v>
       </c>
       <c r="D40" s="4">
-        <v>164167</v>
+        <v>169963</v>
       </c>
       <c r="E40" s="4">
-        <v>180656</v>
+        <v>187296</v>
       </c>
       <c r="F40" s="4">
-        <v>161857</v>
+        <v>167536</v>
       </c>
       <c r="G40" s="4">
-        <v>195903</v>
+        <v>203320</v>
       </c>
       <c r="H40" s="4">
-        <v>223143</v>
+        <v>229315</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10285,25 +10302,25 @@
         <v>134</v>
       </c>
       <c r="B41" s="4">
-        <v>168379</v>
+        <v>174279</v>
       </c>
       <c r="C41" s="4">
-        <v>170857</v>
+        <v>176885</v>
       </c>
       <c r="D41" s="4">
-        <v>175503</v>
+        <v>181766</v>
       </c>
       <c r="E41" s="4">
-        <v>197380</v>
+        <v>204762</v>
       </c>
       <c r="F41" s="4">
-        <v>172320</v>
+        <v>178420</v>
       </c>
       <c r="G41" s="4">
-        <v>217680</v>
+        <v>226098</v>
       </c>
       <c r="H41" s="4">
-        <v>240801</v>
+        <v>247560</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10311,25 +10328,25 @@
         <v>135</v>
       </c>
       <c r="B42" s="4">
-        <v>177903</v>
+        <v>184177</v>
       </c>
       <c r="C42" s="4">
-        <v>180983</v>
+        <v>187412</v>
       </c>
       <c r="D42" s="4">
-        <v>186840</v>
+        <v>193569</v>
       </c>
       <c r="E42" s="4">
-        <v>214498</v>
+        <v>222639</v>
       </c>
       <c r="F42" s="4">
-        <v>182782</v>
+        <v>189305</v>
       </c>
       <c r="G42" s="4">
-        <v>239460</v>
+        <v>248878</v>
       </c>
       <c r="H42" s="4">
-        <v>258464</v>
+        <v>265805</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10337,25 +10354,25 @@
         <v>136</v>
       </c>
       <c r="B43" s="4">
-        <v>187435</v>
+        <v>194082</v>
       </c>
       <c r="C43" s="4">
-        <v>191115</v>
+        <v>197948</v>
       </c>
       <c r="D43" s="4">
-        <v>198185</v>
+        <v>205381</v>
       </c>
       <c r="E43" s="4">
-        <v>231362</v>
+        <v>240252</v>
       </c>
       <c r="F43" s="4">
-        <v>193254</v>
+        <v>200197</v>
       </c>
       <c r="G43" s="4">
-        <v>261247</v>
+        <v>271663</v>
       </c>
       <c r="H43" s="4">
-        <v>276131</v>
+        <v>284058</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10363,25 +10380,25 @@
         <v>137</v>
       </c>
       <c r="B44" s="4">
-        <v>196964</v>
+        <v>203983</v>
       </c>
       <c r="C44" s="4">
-        <v>201256</v>
+        <v>208494</v>
       </c>
       <c r="D44" s="4">
-        <v>209539</v>
+        <v>217202</v>
       </c>
       <c r="E44" s="4">
-        <v>248234</v>
+        <v>257873</v>
       </c>
       <c r="F44" s="4">
-        <v>203734</v>
+        <v>211099</v>
       </c>
       <c r="G44" s="4">
-        <v>283043</v>
+        <v>294461</v>
       </c>
       <c r="H44" s="4">
-        <v>293807</v>
+        <v>302322</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10389,25 +10406,25 @@
         <v>138</v>
       </c>
       <c r="B45" s="4">
-        <v>206487</v>
+        <v>213879</v>
       </c>
       <c r="C45" s="4">
-        <v>211378</v>
+        <v>219020</v>
       </c>
       <c r="D45" s="4">
-        <v>220876</v>
+        <v>229004</v>
       </c>
       <c r="E45" s="4">
-        <v>265089</v>
+        <v>275475</v>
       </c>
       <c r="F45" s="4">
-        <v>214197</v>
+        <v>221983</v>
       </c>
       <c r="G45" s="4">
-        <v>304822</v>
+        <v>317238</v>
       </c>
       <c r="H45" s="4">
-        <v>311464</v>
+        <v>320564</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10415,25 +10432,25 @@
         <v>139</v>
       </c>
       <c r="B46" s="4">
-        <v>216018</v>
+        <v>223785</v>
       </c>
       <c r="C46" s="4">
-        <v>221510</v>
+        <v>229557</v>
       </c>
       <c r="D46" s="4">
-        <v>232209</v>
+        <v>240801</v>
       </c>
       <c r="E46" s="4">
-        <v>281953</v>
+        <v>293088</v>
       </c>
       <c r="F46" s="4">
-        <v>224668</v>
+        <v>232876</v>
       </c>
       <c r="G46" s="4">
-        <v>326609</v>
+        <v>340026</v>
       </c>
       <c r="H46" s="4">
-        <v>329132</v>
+        <v>338819</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10441,25 +10458,25 @@
         <v>140</v>
       </c>
       <c r="B47" s="4">
-        <v>166527</v>
+        <v>172333</v>
       </c>
       <c r="C47" s="4">
-        <v>168640</v>
+        <v>174553</v>
       </c>
       <c r="D47" s="4">
-        <v>172502</v>
+        <v>178612</v>
       </c>
       <c r="E47" s="4">
-        <v>191053</v>
+        <v>198112</v>
       </c>
       <c r="F47" s="4">
-        <v>169905</v>
+        <v>175884</v>
       </c>
       <c r="G47" s="4">
-        <v>208209</v>
+        <v>216143</v>
       </c>
       <c r="H47" s="4">
-        <v>236367</v>
+        <v>242898</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10467,25 +10484,25 @@
         <v>141</v>
       </c>
       <c r="B48" s="4">
-        <v>176417</v>
+        <v>182613</v>
       </c>
       <c r="C48" s="4">
-        <v>179208</v>
+        <v>185548</v>
       </c>
       <c r="D48" s="4">
-        <v>184439</v>
+        <v>191047</v>
       </c>
       <c r="E48" s="4">
-        <v>209045</v>
+        <v>216908</v>
       </c>
       <c r="F48" s="4">
-        <v>180852</v>
+        <v>187275</v>
       </c>
       <c r="G48" s="4">
-        <v>231883</v>
+        <v>240913</v>
       </c>
       <c r="H48" s="4">
-        <v>254914</v>
+        <v>262076</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10493,25 +10510,25 @@
         <v>142</v>
       </c>
       <c r="B49" s="4">
-        <v>186327</v>
+        <v>192915</v>
       </c>
       <c r="C49" s="4">
-        <v>189783</v>
+        <v>196550</v>
       </c>
       <c r="D49" s="4">
-        <v>196384</v>
+        <v>203488</v>
       </c>
       <c r="E49" s="4">
-        <v>227566</v>
+        <v>236261</v>
       </c>
       <c r="F49" s="4">
-        <v>191806</v>
+        <v>198675</v>
       </c>
       <c r="G49" s="4">
-        <v>255565</v>
+        <v>265690</v>
       </c>
       <c r="H49" s="4">
-        <v>273468</v>
+        <v>281262</v>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10519,25 +10536,25 @@
         <v>143</v>
       </c>
       <c r="B50" s="4">
-        <v>196233</v>
+        <v>203215</v>
       </c>
       <c r="C50" s="4">
-        <v>200369</v>
+        <v>207562</v>
       </c>
       <c r="D50" s="4">
-        <v>208340</v>
+        <v>215939</v>
       </c>
       <c r="E50" s="4">
-        <v>245703</v>
+        <v>255212</v>
       </c>
       <c r="F50" s="4">
-        <v>202769</v>
+        <v>210084</v>
       </c>
       <c r="G50" s="4">
-        <v>279255</v>
+        <v>290478</v>
       </c>
       <c r="H50" s="4">
-        <v>292033</v>
+        <v>300458</v>
       </c>
     </row>
     <row r="51" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10545,25 +10562,25 @@
         <v>144</v>
       </c>
       <c r="B51" s="4">
-        <v>206108</v>
+        <v>213481</v>
       </c>
       <c r="C51" s="4">
-        <v>210935</v>
+        <v>218555</v>
       </c>
       <c r="D51" s="4">
-        <v>220276</v>
+        <v>228373</v>
       </c>
       <c r="E51" s="4">
-        <v>263824</v>
+        <v>274144</v>
       </c>
       <c r="F51" s="4">
-        <v>213713</v>
+        <v>221476</v>
       </c>
       <c r="G51" s="4">
-        <v>302928</v>
+        <v>315246</v>
       </c>
       <c r="H51" s="4">
-        <v>310577</v>
+        <v>319634</v>
       </c>
     </row>
     <row r="52" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10571,25 +10588,25 @@
         <v>145</v>
       </c>
       <c r="B52" s="4">
-        <v>216018</v>
+        <v>223785</v>
       </c>
       <c r="C52" s="4">
-        <v>221510</v>
+        <v>229557</v>
       </c>
       <c r="D52" s="4">
-        <v>232209</v>
+        <v>240801</v>
       </c>
       <c r="E52" s="4">
-        <v>281953</v>
+        <v>293088</v>
       </c>
       <c r="F52" s="4">
-        <v>224668</v>
+        <v>232876</v>
       </c>
       <c r="G52" s="4">
-        <v>326609</v>
+        <v>340026</v>
       </c>
       <c r="H52" s="4">
-        <v>329132</v>
+        <v>338819</v>
       </c>
     </row>
     <row r="53" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10597,25 +10614,25 @@
         <v>25</v>
       </c>
       <c r="B53" s="4">
-        <v>225920</v>
+        <v>234080</v>
       </c>
       <c r="C53" s="4">
-        <v>231400</v>
+        <v>239839</v>
       </c>
       <c r="D53" s="4">
-        <v>244133</v>
+        <v>253222</v>
       </c>
       <c r="E53" s="4">
-        <v>299383</v>
+        <v>311295</v>
       </c>
       <c r="F53" s="4">
-        <v>235614</v>
+        <v>244268</v>
       </c>
       <c r="G53" s="4">
-        <v>350283</v>
+        <v>364795</v>
       </c>
       <c r="H53" s="4">
-        <v>346322</v>
+        <v>356572</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10623,25 +10640,25 @@
         <v>146</v>
       </c>
       <c r="B54" s="4">
-        <v>174198</v>
+        <v>180282</v>
       </c>
       <c r="C54" s="4">
-        <v>176546</v>
+        <v>182750</v>
       </c>
       <c r="D54" s="4">
-        <v>180852</v>
+        <v>187275</v>
       </c>
       <c r="E54" s="4">
-        <v>201412</v>
+        <v>208886</v>
       </c>
       <c r="F54" s="4">
-        <v>177903</v>
+        <v>184177</v>
       </c>
       <c r="G54" s="4">
-        <v>220424</v>
+        <v>228868</v>
       </c>
       <c r="H54" s="4">
-        <v>249590</v>
+        <v>256481</v>
       </c>
     </row>
     <row r="55" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10649,25 +10666,25 @@
         <v>147</v>
       </c>
       <c r="B55" s="4">
-        <v>184474</v>
+        <v>190969</v>
       </c>
       <c r="C55" s="4">
-        <v>187592</v>
+        <v>194246</v>
       </c>
       <c r="D55" s="4">
-        <v>193332</v>
+        <v>200279</v>
       </c>
       <c r="E55" s="4">
-        <v>220756</v>
+        <v>229103</v>
       </c>
       <c r="F55" s="4">
-        <v>189405</v>
+        <v>196151</v>
       </c>
       <c r="G55" s="4">
-        <v>246110</v>
+        <v>255752</v>
       </c>
       <c r="H55" s="4">
-        <v>269085</v>
+        <v>276654</v>
       </c>
     </row>
     <row r="56" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10675,25 +10692,25 @@
         <v>148</v>
       </c>
       <c r="B56" s="4">
-        <v>194758</v>
+        <v>201666</v>
       </c>
       <c r="C56" s="4">
-        <v>198659</v>
+        <v>205765</v>
       </c>
       <c r="D56" s="4">
-        <v>205822</v>
+        <v>213293</v>
       </c>
       <c r="E56" s="4">
-        <v>240107</v>
+        <v>249330</v>
       </c>
       <c r="F56" s="4">
-        <v>200916</v>
+        <v>208137</v>
       </c>
       <c r="G56" s="4">
-        <v>271803</v>
+        <v>282646</v>
       </c>
       <c r="H56" s="4">
-        <v>288614</v>
+        <v>296865</v>
       </c>
     </row>
     <row r="57" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10701,25 +10718,25 @@
         <v>149</v>
       </c>
       <c r="B57" s="4">
-        <v>205025</v>
+        <v>212342</v>
       </c>
       <c r="C57" s="4">
-        <v>209696</v>
+        <v>217252</v>
       </c>
       <c r="D57" s="4">
-        <v>218292</v>
+        <v>226288</v>
       </c>
       <c r="E57" s="4">
-        <v>259440</v>
+        <v>269537</v>
       </c>
       <c r="F57" s="4">
-        <v>212409</v>
+        <v>220104</v>
       </c>
       <c r="G57" s="4">
-        <v>297480</v>
+        <v>309520</v>
       </c>
       <c r="H57" s="4">
-        <v>308099</v>
+        <v>317027</v>
       </c>
     </row>
     <row r="58" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10727,25 +10744,25 @@
         <v>150</v>
       </c>
       <c r="B58" s="4">
-        <v>215300</v>
+        <v>223030</v>
       </c>
       <c r="C58" s="4">
-        <v>220741</v>
+        <v>228748</v>
       </c>
       <c r="D58" s="4">
-        <v>230773</v>
+        <v>239293</v>
       </c>
       <c r="E58" s="4">
-        <v>278782</v>
+        <v>289755</v>
       </c>
       <c r="F58" s="4">
-        <v>223911</v>
+        <v>232080</v>
       </c>
       <c r="G58" s="4">
-        <v>323166</v>
+        <v>336406</v>
       </c>
       <c r="H58" s="4">
-        <v>327594</v>
+        <v>337201</v>
       </c>
     </row>
     <row r="59" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10753,25 +10770,25 @@
         <v>151</v>
       </c>
       <c r="B59" s="4">
-        <v>225569</v>
+        <v>233709</v>
       </c>
       <c r="C59" s="4">
-        <v>231778</v>
+        <v>240236</v>
       </c>
       <c r="D59" s="4">
-        <v>243247</v>
+        <v>252290</v>
       </c>
       <c r="E59" s="4">
-        <v>298118</v>
+        <v>309965</v>
       </c>
       <c r="F59" s="4">
-        <v>235405</v>
+        <v>244049</v>
       </c>
       <c r="G59" s="4">
-        <v>348843</v>
+        <v>363281</v>
       </c>
       <c r="H59" s="4">
-        <v>347078</v>
+        <v>357366</v>
       </c>
     </row>
     <row r="60" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10779,25 +10796,25 @@
         <v>32</v>
       </c>
       <c r="B60" s="4">
-        <v>235862</v>
+        <v>244414</v>
       </c>
       <c r="C60" s="4">
-        <v>242842</v>
+        <v>251750</v>
       </c>
       <c r="D60" s="4">
-        <v>255744</v>
+        <v>265312</v>
       </c>
       <c r="E60" s="4">
-        <v>317478</v>
+        <v>330199</v>
       </c>
       <c r="F60" s="4">
-        <v>246925</v>
+        <v>256041</v>
       </c>
       <c r="G60" s="4">
-        <v>374547</v>
+        <v>390183</v>
       </c>
       <c r="H60" s="4">
-        <v>366591</v>
+        <v>377557</v>
       </c>
     </row>
     <row r="61" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10805,25 +10822,25 @@
         <v>152</v>
       </c>
       <c r="B61" s="4">
-        <v>180792</v>
+        <v>187118</v>
       </c>
       <c r="C61" s="4">
-        <v>183363</v>
+        <v>189819</v>
       </c>
       <c r="D61" s="4">
-        <v>188098</v>
+        <v>194797</v>
       </c>
       <c r="E61" s="4">
-        <v>210720</v>
+        <v>218574</v>
       </c>
       <c r="F61" s="4">
-        <v>184849</v>
+        <v>191383</v>
       </c>
       <c r="G61" s="4">
-        <v>231626</v>
+        <v>240548</v>
       </c>
       <c r="H61" s="4">
-        <v>261725</v>
+        <v>268936</v>
       </c>
     </row>
     <row r="62" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10831,25 +10848,25 @@
         <v>153</v>
       </c>
       <c r="B62" s="4">
-        <v>191617</v>
+        <v>198380</v>
       </c>
       <c r="C62" s="4">
-        <v>195048</v>
+        <v>201986</v>
       </c>
       <c r="D62" s="4">
-        <v>201362</v>
+        <v>208623</v>
       </c>
       <c r="E62" s="4">
-        <v>231524</v>
+        <v>240326</v>
       </c>
       <c r="F62" s="4">
-        <v>197030</v>
+        <v>204070</v>
       </c>
       <c r="G62" s="4">
-        <v>259404</v>
+        <v>269630</v>
       </c>
       <c r="H62" s="4">
-        <v>282316</v>
+        <v>290261</v>
       </c>
     </row>
     <row r="63" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10857,25 +10874,25 @@
         <v>154</v>
       </c>
       <c r="B63" s="4">
-        <v>203365</v>
+        <v>210594</v>
       </c>
       <c r="C63" s="4">
-        <v>207657</v>
+        <v>215105</v>
       </c>
       <c r="D63" s="4">
-        <v>215550</v>
+        <v>223402</v>
       </c>
       <c r="E63" s="4">
-        <v>253253</v>
+        <v>263031</v>
       </c>
       <c r="F63" s="4">
-        <v>210135</v>
+        <v>217711</v>
       </c>
       <c r="G63" s="4">
-        <v>288107</v>
+        <v>299665</v>
       </c>
       <c r="H63" s="4">
-        <v>303829</v>
+        <v>312536</v>
       </c>
     </row>
     <row r="64" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10883,25 +10900,25 @@
         <v>155</v>
       </c>
       <c r="B64" s="4">
-        <v>215164</v>
+        <v>222864</v>
       </c>
       <c r="C64" s="4">
-        <v>220317</v>
+        <v>228281</v>
       </c>
       <c r="D64" s="4">
-        <v>229789</v>
+        <v>238236</v>
       </c>
       <c r="E64" s="4">
-        <v>275033</v>
+        <v>285791</v>
       </c>
       <c r="F64" s="4">
-        <v>223292</v>
+        <v>231408</v>
       </c>
       <c r="G64" s="4">
-        <v>316861</v>
+        <v>329756</v>
       </c>
       <c r="H64" s="4">
-        <v>325395</v>
+        <v>334869</v>
       </c>
     </row>
     <row r="65" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10909,25 +10926,25 @@
         <v>156</v>
       </c>
       <c r="B65" s="4">
-        <v>224185</v>
+        <v>232260</v>
       </c>
       <c r="C65" s="4">
-        <v>230199</v>
+        <v>238582</v>
       </c>
       <c r="D65" s="4">
-        <v>241250</v>
+        <v>250195</v>
       </c>
       <c r="E65" s="4">
-        <v>294034</v>
+        <v>305677</v>
       </c>
       <c r="F65" s="4">
-        <v>233670</v>
+        <v>242229</v>
       </c>
       <c r="G65" s="4">
-        <v>342836</v>
+        <v>356972</v>
       </c>
       <c r="H65" s="4">
-        <v>344182</v>
+        <v>354328</v>
       </c>
     </row>
     <row r="66" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10935,25 +10952,25 @@
         <v>157</v>
       </c>
       <c r="B66" s="4">
-        <v>234521</v>
+        <v>243015</v>
       </c>
       <c r="C66" s="4">
-        <v>241396</v>
+        <v>250241</v>
       </c>
       <c r="D66" s="4">
-        <v>254024</v>
+        <v>263515</v>
       </c>
       <c r="E66" s="4">
-        <v>314350</v>
+        <v>326922</v>
       </c>
       <c r="F66" s="4">
-        <v>245362</v>
+        <v>254410</v>
       </c>
       <c r="G66" s="4">
-        <v>370127</v>
+        <v>385547</v>
       </c>
       <c r="H66" s="4">
-        <v>364284</v>
+        <v>375144</v>
       </c>
     </row>
     <row r="67" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10961,25 +10978,25 @@
         <v>38</v>
       </c>
       <c r="B67" s="4">
-        <v>245858</v>
+        <v>254807</v>
       </c>
       <c r="C67" s="4">
-        <v>253595</v>
+        <v>262939</v>
       </c>
       <c r="D67" s="4">
-        <v>267802</v>
+        <v>277871</v>
       </c>
       <c r="E67" s="4">
-        <v>335669</v>
+        <v>349203</v>
       </c>
       <c r="F67" s="4">
-        <v>258057</v>
+        <v>267628</v>
       </c>
       <c r="G67" s="4">
-        <v>398419</v>
+        <v>415160</v>
       </c>
       <c r="H67" s="4">
-        <v>385389</v>
+        <v>396999</v>
       </c>
     </row>
     <row r="68" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10987,25 +11004,25 @@
         <v>158</v>
       </c>
       <c r="B68" s="4">
-        <v>204931</v>
+        <v>212132</v>
       </c>
       <c r="C68" s="4">
-        <v>208207</v>
+        <v>215573</v>
       </c>
       <c r="D68" s="4">
-        <v>214234</v>
+        <v>221909</v>
       </c>
       <c r="E68" s="4">
-        <v>243026</v>
+        <v>252172</v>
       </c>
       <c r="F68" s="4">
-        <v>210111</v>
+        <v>217576</v>
       </c>
       <c r="G68" s="4">
-        <v>269642</v>
+        <v>280148</v>
       </c>
       <c r="H68" s="4">
-        <v>302522</v>
+        <v>310848</v>
       </c>
     </row>
     <row r="69" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11013,25 +11030,25 @@
         <v>159</v>
       </c>
       <c r="B69" s="4">
-        <v>216676</v>
+        <v>224363</v>
       </c>
       <c r="C69" s="4">
-        <v>221046</v>
+        <v>228956</v>
       </c>
       <c r="D69" s="4">
-        <v>229083</v>
+        <v>237403</v>
       </c>
       <c r="E69" s="4">
-        <v>267465</v>
+        <v>277746</v>
       </c>
       <c r="F69" s="4">
-        <v>223577</v>
+        <v>231617</v>
       </c>
       <c r="G69" s="4">
-        <v>302947</v>
+        <v>315041</v>
       </c>
       <c r="H69" s="4">
-        <v>325610</v>
+        <v>334801</v>
       </c>
     </row>
     <row r="70" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11039,25 +11056,25 @@
         <v>160</v>
       </c>
       <c r="B70" s="4">
-        <v>228438</v>
+        <v>236613</v>
       </c>
       <c r="C70" s="4">
-        <v>233905</v>
+        <v>242358</v>
       </c>
       <c r="D70" s="4">
-        <v>243950</v>
+        <v>252917</v>
       </c>
       <c r="E70" s="4">
-        <v>291921</v>
+        <v>303338</v>
       </c>
       <c r="F70" s="4">
-        <v>237062</v>
+        <v>245676</v>
       </c>
       <c r="G70" s="4">
-        <v>336270</v>
+        <v>349951</v>
       </c>
       <c r="H70" s="4">
-        <v>348719</v>
+        <v>358774</v>
       </c>
     </row>
     <row r="71" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11065,25 +11082,25 @@
         <v>161</v>
       </c>
       <c r="B71" s="4">
-        <v>240146</v>
+        <v>248805</v>
       </c>
       <c r="C71" s="4">
-        <v>246708</v>
+        <v>255703</v>
       </c>
       <c r="D71" s="4">
-        <v>258763</v>
+        <v>268372</v>
       </c>
       <c r="E71" s="4">
-        <v>316323</v>
+        <v>328873</v>
       </c>
       <c r="F71" s="4">
-        <v>250492</v>
+        <v>259680</v>
       </c>
       <c r="G71" s="4">
-        <v>369537</v>
+        <v>384805</v>
       </c>
       <c r="H71" s="4">
-        <v>371770</v>
+        <v>382688</v>
       </c>
     </row>
     <row r="72" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11091,25 +11108,25 @@
         <v>162</v>
       </c>
       <c r="B72" s="4">
-        <v>251928</v>
+        <v>261074</v>
       </c>
       <c r="C72" s="4">
-        <v>259586</v>
+        <v>269123</v>
       </c>
       <c r="D72" s="4">
-        <v>273650</v>
+        <v>283906</v>
       </c>
       <c r="E72" s="4">
-        <v>340797</v>
+        <v>354484</v>
       </c>
       <c r="F72" s="4">
-        <v>263996</v>
+        <v>273759</v>
       </c>
       <c r="G72" s="4">
-        <v>393016</v>
+        <v>409370</v>
       </c>
       <c r="H72" s="4">
-        <v>394896</v>
+        <v>406676</v>
       </c>
     </row>
     <row r="73" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11117,25 +11134,25 @@
         <v>163</v>
       </c>
       <c r="B73" s="4">
-        <v>263686</v>
+        <v>273318</v>
       </c>
       <c r="C73" s="4">
-        <v>272439</v>
+        <v>282519</v>
       </c>
       <c r="D73" s="4">
-        <v>288512</v>
+        <v>299413</v>
       </c>
       <c r="E73" s="4">
-        <v>365249</v>
+        <v>380070</v>
       </c>
       <c r="F73" s="4">
-        <v>277475</v>
+        <v>287812</v>
       </c>
       <c r="G73" s="4">
-        <v>416471</v>
+        <v>433908</v>
       </c>
       <c r="H73" s="4">
-        <v>417997</v>
+        <v>430642</v>
       </c>
     </row>
     <row r="74" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11143,25 +11160,25 @@
         <v>45</v>
       </c>
       <c r="B74" s="4">
-        <v>275432</v>
+        <v>285554</v>
       </c>
       <c r="C74" s="4">
-        <v>285282</v>
+        <v>295908</v>
       </c>
       <c r="D74" s="4">
-        <v>303365</v>
+        <v>314913</v>
       </c>
       <c r="E74" s="4">
-        <v>389691</v>
+        <v>405648</v>
       </c>
       <c r="F74" s="4">
-        <v>290944</v>
+        <v>301858</v>
       </c>
       <c r="G74" s="4">
-        <v>449778</v>
+        <v>468805</v>
       </c>
       <c r="H74" s="4">
-        <v>441091</v>
+        <v>454601</v>
       </c>
     </row>
   </sheetData>
@@ -11238,22 +11255,22 @@
         <v>169</v>
       </c>
       <c r="C6" s="4">
-        <v>371415</v>
+        <v>383498</v>
       </c>
       <c r="D6" s="4">
-        <v>382373</v>
+        <v>395028</v>
       </c>
       <c r="E6" s="4">
-        <v>374894</v>
+        <v>387158</v>
       </c>
       <c r="F6" s="4">
-        <v>435361</v>
+        <v>450784</v>
       </c>
       <c r="G6" s="4">
-        <v>484266</v>
+        <v>502244</v>
       </c>
       <c r="H6" s="4">
-        <v>496408</v>
+        <v>510299</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11264,16 +11281,16 @@
         <v>169</v>
       </c>
       <c r="C7" s="4">
-        <v>407141</v>
+        <v>420314</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>169</v>
       </c>
       <c r="E7" s="4">
-        <v>410621</v>
+        <v>423974</v>
       </c>
       <c r="F7" s="4">
-        <v>471088</v>
+        <v>487600</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>169</v>
@@ -11287,25 +11304,25 @@
         <v>171</v>
       </c>
       <c r="B8" s="4">
-        <v>376727</v>
+        <v>388808</v>
       </c>
       <c r="C8" s="4">
-        <v>382467</v>
+        <v>394848</v>
       </c>
       <c r="D8" s="4">
-        <v>392833</v>
+        <v>405755</v>
       </c>
       <c r="E8" s="4">
-        <v>385751</v>
+        <v>398304</v>
       </c>
       <c r="F8" s="4">
-        <v>443039</v>
+        <v>458585</v>
       </c>
       <c r="G8" s="4">
-        <v>489360</v>
+        <v>507326</v>
       </c>
       <c r="H8" s="4">
-        <v>531487</v>
+        <v>545580</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11313,25 +11330,25 @@
         <v>172</v>
       </c>
       <c r="B9" s="4">
-        <v>427524</v>
+        <v>440861</v>
       </c>
       <c r="C9" s="4">
-        <v>430394</v>
+        <v>443881</v>
       </c>
       <c r="D9" s="4">
-        <v>435576</v>
+        <v>449335</v>
       </c>
       <c r="E9" s="4">
-        <v>432035</v>
+        <v>445608</v>
       </c>
       <c r="F9" s="4">
-        <v>460680</v>
+        <v>475749</v>
       </c>
       <c r="G9" s="4">
-        <v>483840</v>
+        <v>500120</v>
       </c>
       <c r="H9" s="4">
-        <v>504904</v>
+        <v>519247</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11339,7 +11356,7 @@
         <v>173</v>
       </c>
       <c r="B10" s="4">
-        <v>447532</v>
+        <v>461479</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>169</v>
@@ -11348,10 +11365,10 @@
         <v>169</v>
       </c>
       <c r="E10" s="4">
-        <v>452043</v>
+        <v>466226</v>
       </c>
       <c r="F10" s="4">
-        <v>480688</v>
+        <v>496366</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>169</v>
@@ -11365,25 +11382,25 @@
         <v>174</v>
       </c>
       <c r="B11" s="4">
-        <v>443000</v>
+        <v>456679</v>
       </c>
       <c r="C11" s="4">
-        <v>444546</v>
+        <v>458306</v>
       </c>
       <c r="D11" s="4">
-        <v>447433</v>
+        <v>461343</v>
       </c>
       <c r="E11" s="4">
-        <v>445463</v>
+        <v>459272</v>
       </c>
       <c r="F11" s="4">
-        <v>461375</v>
+        <v>476014</v>
       </c>
       <c r="G11" s="4">
-        <v>474242</v>
+        <v>489553</v>
       </c>
       <c r="H11" s="4">
-        <v>495624</v>
+        <v>509859</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11391,7 +11408,7 @@
         <v>175</v>
       </c>
       <c r="B12" s="4">
-        <v>454433</v>
+        <v>468461</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>169</v>
@@ -11400,10 +11417,10 @@
         <v>169</v>
       </c>
       <c r="E12" s="4">
-        <v>456896</v>
+        <v>471053</v>
       </c>
       <c r="F12" s="4">
-        <v>472808</v>
+        <v>487795</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>169</v>
@@ -11417,7 +11434,7 @@
         <v>176</v>
       </c>
       <c r="B13" s="4">
-        <v>465460</v>
+        <v>479661</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>169</v>
@@ -11443,25 +11460,25 @@
         <v>177</v>
       </c>
       <c r="B14" s="4">
-        <v>460393</v>
+        <v>474732</v>
       </c>
       <c r="C14" s="4">
-        <v>463263</v>
+        <v>477752</v>
       </c>
       <c r="D14" s="4">
-        <v>468445</v>
+        <v>483206</v>
       </c>
       <c r="E14" s="4">
-        <v>464904</v>
+        <v>479479</v>
       </c>
       <c r="F14" s="4">
-        <v>493549</v>
+        <v>509620</v>
       </c>
       <c r="G14" s="4">
-        <v>516709</v>
+        <v>533991</v>
       </c>
       <c r="H14" s="4">
-        <v>602362</v>
+        <v>617707</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11469,25 +11486,25 @@
         <v>178</v>
       </c>
       <c r="B15" s="4">
-        <v>455862</v>
+        <v>469933</v>
       </c>
       <c r="C15" s="4">
-        <v>457407</v>
+        <v>471559</v>
       </c>
       <c r="D15" s="4">
-        <v>460295</v>
+        <v>474597</v>
       </c>
       <c r="E15" s="4">
-        <v>458325</v>
+        <v>472526</v>
       </c>
       <c r="F15" s="4">
-        <v>474236</v>
+        <v>489268</v>
       </c>
       <c r="G15" s="4">
-        <v>487103</v>
+        <v>502807</v>
       </c>
       <c r="H15" s="4">
-        <v>540780</v>
+        <v>555408</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11495,25 +11512,25 @@
         <v>179</v>
       </c>
       <c r="B16" s="4">
-        <v>405629</v>
+        <v>418660</v>
       </c>
       <c r="C16" s="4">
-        <v>411810</v>
+        <v>425164</v>
       </c>
       <c r="D16" s="4">
-        <v>423359</v>
+        <v>437317</v>
       </c>
       <c r="E16" s="4">
-        <v>415483</v>
+        <v>429029</v>
       </c>
       <c r="F16" s="4">
-        <v>479128</v>
+        <v>496000</v>
       </c>
       <c r="G16" s="4">
-        <v>530596</v>
+        <v>550156</v>
       </c>
       <c r="H16" s="4">
-        <v>616122</v>
+        <v>631376</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11521,25 +11538,25 @@
         <v>180</v>
       </c>
       <c r="B17" s="4">
-        <v>467826</v>
+        <v>482304</v>
       </c>
       <c r="C17" s="4">
-        <v>469838</v>
+        <v>484422</v>
       </c>
       <c r="D17" s="4">
-        <v>473494</v>
+        <v>488269</v>
       </c>
       <c r="E17" s="4">
-        <v>471031</v>
+        <v>485677</v>
       </c>
       <c r="F17" s="4">
-        <v>491163</v>
+        <v>506861</v>
       </c>
       <c r="G17" s="4">
-        <v>507459</v>
+        <v>524009</v>
       </c>
       <c r="H17" s="4">
-        <v>557253</v>
+        <v>572440</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11547,25 +11564,25 @@
         <v>181</v>
       </c>
       <c r="B18" s="4">
-        <v>473286</v>
+        <v>487839</v>
       </c>
       <c r="C18" s="4">
-        <v>475307</v>
+        <v>489966</v>
       </c>
       <c r="D18" s="4">
-        <v>477612</v>
+        <v>492391</v>
       </c>
       <c r="E18" s="4">
-        <v>476040</v>
+        <v>490738</v>
       </c>
       <c r="F18" s="4">
-        <v>488773</v>
+        <v>504135</v>
       </c>
       <c r="G18" s="4">
-        <v>499056</v>
+        <v>514956</v>
       </c>
       <c r="H18" s="4">
-        <v>526180</v>
+        <v>541220</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11573,7 +11590,7 @@
         <v>182</v>
       </c>
       <c r="B19" s="4">
-        <v>538402</v>
+        <v>554941</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>169</v>
@@ -11582,10 +11599,10 @@
         <v>169</v>
       </c>
       <c r="E19" s="4">
-        <v>541156</v>
+        <v>557840</v>
       </c>
       <c r="F19" s="4">
-        <v>553889</v>
+        <v>571237</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>169</v>
@@ -11599,25 +11616,25 @@
         <v>183</v>
       </c>
       <c r="B20" s="4">
-        <v>450342</v>
+        <v>464538</v>
       </c>
       <c r="C20" s="4">
-        <v>456602</v>
+        <v>471126</v>
       </c>
       <c r="D20" s="4">
-        <v>465255</v>
+        <v>480231</v>
       </c>
       <c r="E20" s="4">
-        <v>459358</v>
+        <v>474025</v>
       </c>
       <c r="F20" s="4">
-        <v>507100</v>
+        <v>524261</v>
       </c>
       <c r="G20" s="4">
-        <v>545703</v>
+        <v>564881</v>
       </c>
       <c r="H20" s="4">
-        <v>655049</v>
+        <v>670999</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11625,25 +11642,25 @@
         <v>184</v>
       </c>
       <c r="B21" s="4">
-        <v>407887</v>
+        <v>420787</v>
       </c>
       <c r="C21" s="4">
-        <v>414148</v>
+        <v>427376</v>
       </c>
       <c r="D21" s="4">
-        <v>422801</v>
+        <v>436481</v>
       </c>
       <c r="E21" s="4">
-        <v>416903</v>
+        <v>430274</v>
       </c>
       <c r="F21" s="4">
-        <v>464645</v>
+        <v>480511</v>
       </c>
       <c r="G21" s="4">
-        <v>503248</v>
+        <v>521131</v>
       </c>
       <c r="H21" s="4">
-        <v>515710</v>
+        <v>530364</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11651,7 +11668,7 @@
         <v>204</v>
       </c>
       <c r="B22" s="4">
-        <v>501187</v>
+        <v>516477</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>169</v>
@@ -11724,13 +11741,13 @@
         <v>206</v>
       </c>
       <c r="B6" s="4">
-        <v>205841</v>
+        <v>270825</v>
       </c>
       <c r="C6" s="4">
-        <v>306301</v>
+        <v>420944</v>
       </c>
       <c r="D6" s="4">
-        <v>251990</v>
+        <v>213493</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11738,13 +11755,13 @@
         <v>207</v>
       </c>
       <c r="B7" s="4">
-        <v>222833</v>
+        <v>295004</v>
       </c>
       <c r="C7" s="4">
-        <v>336456</v>
+        <v>469647</v>
       </c>
       <c r="D7" s="4">
-        <v>279619</v>
+        <v>231142</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11752,13 +11769,13 @@
         <v>208</v>
       </c>
       <c r="B8" s="4">
-        <v>240198</v>
+        <v>317255</v>
       </c>
       <c r="C8" s="4">
-        <v>369217</v>
+        <v>521016</v>
       </c>
       <c r="D8" s="4">
-        <v>309753</v>
+        <v>249213</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11766,13 +11783,13 @@
         <v>209</v>
       </c>
       <c r="B9" s="4">
-        <v>251984</v>
+        <v>332305</v>
       </c>
       <c r="C9" s="4">
-        <v>391270</v>
+        <v>555473</v>
       </c>
       <c r="D9" s="4">
-        <v>330045</v>
+        <v>261480</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11780,13 +11797,13 @@
         <v>132</v>
       </c>
       <c r="B10" s="4">
-        <v>217036</v>
+        <v>287867</v>
       </c>
       <c r="C10" s="4">
-        <v>325247</v>
+        <v>451296</v>
       </c>
       <c r="D10" s="4">
-        <v>268413</v>
+        <v>225104</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11794,13 +11811,13 @@
         <v>210</v>
       </c>
       <c r="B11" s="4">
-        <v>230215</v>
+        <v>303105</v>
       </c>
       <c r="C11" s="4">
-        <v>349903</v>
+        <v>490202</v>
       </c>
       <c r="D11" s="4">
-        <v>292936</v>
+        <v>238832</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11808,13 +11825,13 @@
         <v>211</v>
       </c>
       <c r="B12" s="4">
-        <v>250382</v>
+        <v>327985</v>
       </c>
       <c r="C12" s="4">
-        <v>385731</v>
+        <v>545712</v>
       </c>
       <c r="D12" s="4">
-        <v>327045</v>
+        <v>259810</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11822,13 +11839,13 @@
         <v>212</v>
       </c>
       <c r="B13" s="4">
-        <v>269557</v>
+        <v>350236</v>
       </c>
       <c r="C13" s="4">
-        <v>422112</v>
+        <v>603431</v>
       </c>
       <c r="D13" s="4">
-        <v>363212</v>
+        <v>279787</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11836,13 +11853,13 @@
         <v>213</v>
       </c>
       <c r="B14" s="4">
-        <v>282553</v>
+        <v>365285</v>
       </c>
       <c r="C14" s="4">
-        <v>446585</v>
+        <v>642157</v>
       </c>
       <c r="D14" s="4">
-        <v>387562</v>
+        <v>293325</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11850,13 +11867,13 @@
         <v>25</v>
       </c>
       <c r="B15" s="4">
-        <v>240973</v>
+        <v>320848</v>
       </c>
       <c r="C15" s="4">
-        <v>367298</v>
+        <v>512906</v>
       </c>
       <c r="D15" s="4">
-        <v>302100</v>
+        <v>249972</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11864,13 +11881,13 @@
         <v>26</v>
       </c>
       <c r="B16" s="4">
-        <v>255361</v>
+        <v>336085</v>
       </c>
       <c r="C16" s="4">
-        <v>394373</v>
+        <v>548545</v>
       </c>
       <c r="D16" s="4">
-        <v>323520</v>
+        <v>264972</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11878,13 +11895,13 @@
         <v>27</v>
       </c>
       <c r="B17" s="4">
-        <v>277931</v>
+        <v>360965</v>
       </c>
       <c r="C17" s="4">
-        <v>435007</v>
+        <v>602588</v>
       </c>
       <c r="D17" s="4">
-        <v>356234</v>
+        <v>288478</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11892,13 +11909,13 @@
         <v>28</v>
       </c>
       <c r="B18" s="4">
-        <v>295310</v>
+        <v>379474</v>
       </c>
       <c r="C18" s="4">
-        <v>471411</v>
+        <v>665971</v>
       </c>
       <c r="D18" s="4">
-        <v>397727</v>
+        <v>306628</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11906,13 +11923,13 @@
         <v>29</v>
       </c>
       <c r="B19" s="4">
-        <v>313131</v>
+        <v>398265</v>
       </c>
       <c r="C19" s="4">
-        <v>501919</v>
+        <v>707768</v>
       </c>
       <c r="D19" s="4">
-        <v>425052</v>
+        <v>325181</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11920,13 +11937,13 @@
         <v>32</v>
       </c>
       <c r="B20" s="4">
-        <v>254041</v>
+        <v>337852</v>
       </c>
       <c r="C20" s="4">
-        <v>390025</v>
+        <v>556418</v>
       </c>
       <c r="D20" s="4">
-        <v>331029</v>
+        <v>263553</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11934,13 +11951,13 @@
         <v>33</v>
       </c>
       <c r="B21" s="4">
-        <v>268419</v>
+        <v>353090</v>
       </c>
       <c r="C21" s="4">
-        <v>417080</v>
+        <v>591437</v>
       </c>
       <c r="D21" s="4">
-        <v>351858</v>
+        <v>278544</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11948,13 +11965,13 @@
         <v>34</v>
       </c>
       <c r="B22" s="4">
-        <v>290998</v>
+        <v>377979</v>
       </c>
       <c r="C22" s="4">
-        <v>457723</v>
+        <v>645646</v>
       </c>
       <c r="D22" s="4">
-        <v>384731</v>
+        <v>302059</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11962,13 +11979,13 @@
         <v>35</v>
       </c>
       <c r="B23" s="4">
-        <v>308367</v>
+        <v>396479</v>
       </c>
       <c r="C23" s="4">
-        <v>494116</v>
+        <v>709475</v>
       </c>
       <c r="D23" s="4">
-        <v>426646</v>
+        <v>320198</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11976,13 +11993,13 @@
         <v>79</v>
       </c>
       <c r="B24" s="4">
-        <v>326197</v>
+        <v>415280</v>
       </c>
       <c r="C24" s="4">
-        <v>524633</v>
+        <v>750739</v>
       </c>
       <c r="D24" s="4">
-        <v>453465</v>
+        <v>338762</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11990,13 +12007,13 @@
         <v>38</v>
       </c>
       <c r="B25" s="4">
-        <v>266836</v>
+        <v>354587</v>
       </c>
       <c r="C25" s="4">
-        <v>412469</v>
+        <v>599257</v>
       </c>
       <c r="D25" s="4">
-        <v>359313</v>
+        <v>276854</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12004,13 +12021,13 @@
         <v>39</v>
       </c>
       <c r="B26" s="4">
-        <v>281511</v>
+        <v>370132</v>
       </c>
       <c r="C26" s="4">
-        <v>439821</v>
+        <v>634943</v>
       </c>
       <c r="D26" s="4">
-        <v>380780</v>
+        <v>292151</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12018,13 +12035,13 @@
         <v>40</v>
       </c>
       <c r="B27" s="4">
-        <v>305773</v>
+        <v>396846</v>
       </c>
       <c r="C27" s="4">
-        <v>482067</v>
+        <v>691195</v>
       </c>
       <c r="D27" s="4">
-        <v>415623</v>
+        <v>317408</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12032,13 +12049,13 @@
         <v>41</v>
       </c>
       <c r="B28" s="4">
-        <v>321390</v>
+        <v>413447</v>
       </c>
       <c r="C28" s="4">
-        <v>516789</v>
+        <v>752478</v>
       </c>
       <c r="D28" s="4">
-        <v>455090</v>
+        <v>333732</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12046,13 +12063,13 @@
         <v>42</v>
       </c>
       <c r="B29" s="4">
-        <v>339544</v>
+        <v>432584</v>
       </c>
       <c r="C29" s="4">
-        <v>547629</v>
+        <v>794060</v>
       </c>
       <c r="D29" s="4">
-        <v>482219</v>
+        <v>352632</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12060,13 +12077,13 @@
         <v>45</v>
       </c>
       <c r="B30" s="4">
-        <v>312978</v>
+        <v>413880</v>
       </c>
       <c r="C30" s="4">
-        <v>486533</v>
+        <v>701897</v>
       </c>
       <c r="D30" s="4">
-        <v>419713</v>
+        <v>324768</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12074,13 +12091,13 @@
         <v>46</v>
       </c>
       <c r="B31" s="4">
-        <v>331137</v>
+        <v>429968</v>
       </c>
       <c r="C31" s="4">
-        <v>520328</v>
+        <v>756588</v>
       </c>
       <c r="D31" s="4">
-        <v>459251</v>
+        <v>343722</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12088,13 +12105,13 @@
         <v>47</v>
       </c>
       <c r="B32" s="4">
-        <v>359592</v>
+        <v>456654</v>
       </c>
       <c r="C32" s="4">
-        <v>570988</v>
+        <v>840899</v>
       </c>
       <c r="D32" s="4">
-        <v>520760</v>
+        <v>373392</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12102,13 +12119,13 @@
         <v>48</v>
       </c>
       <c r="B33" s="4">
-        <v>380291</v>
+        <v>473890</v>
       </c>
       <c r="C33" s="4">
-        <v>615258</v>
+        <v>916023</v>
       </c>
       <c r="D33" s="4">
-        <v>573392</v>
+        <v>395053</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12116,13 +12133,13 @@
         <v>49</v>
       </c>
       <c r="B34" s="4">
-        <v>400389</v>
+        <v>491896</v>
       </c>
       <c r="C34" s="4">
-        <v>651081</v>
+        <v>972632</v>
       </c>
       <c r="D34" s="4">
-        <v>614780</v>
+        <v>416017</v>
       </c>
     </row>
   </sheetData>
